--- a/Wasser/Wasserchemie - Multi 3510 IDS (vor Ort)/05 Chemische Parameter.xlsx
+++ b/Wasser/Wasserchemie - Multi 3510 IDS (vor Ort)/05 Chemische Parameter.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Alexandra\Documents\GitHub\Moore-Lichtenau-Meusebach\Wasser\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Alexandra\Documents\GitHub\Moore-Lichtenau-Meusebach\Wasser\Wasserchemie - Multi 3510 IDS (vor Ort)\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D14D4772-2F05-4EA8-BDF7-6AE4E1AE1011}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8ECDCCB-6911-435B-8002-DDA7235B4475}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10140" yWindow="0" windowWidth="10485" windowHeight="10905" firstSheet="2" activeTab="3" xr2:uid="{C748F3ED-3D32-4CFF-8258-545184BF166B}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="3" xr2:uid="{C748F3ED-3D32-4CFF-8258-545184BF166B}"/>
   </bookViews>
   <sheets>
     <sheet name="1_Meusebach trocken" sheetId="4" r:id="rId1"/>
@@ -98,9 +98,6 @@
     <t>MS 4</t>
   </si>
   <si>
-    <t>Wasserproben Bezeichnung</t>
-  </si>
-  <si>
     <t xml:space="preserve">trocken </t>
   </si>
   <si>
@@ -475,6 +472,9 @@
   </si>
   <si>
     <t>24.09-Meu-T-MS-1</t>
+  </si>
+  <si>
+    <t>Wasserproben Beschriftung</t>
   </si>
 </sst>
 </file>
@@ -1181,6 +1181,96 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="14" fontId="0" fillId="2" borderId="27" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="2" borderId="28" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="2" borderId="31" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="2" borderId="38" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="2" borderId="39" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="2" borderId="32" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1190,21 +1280,6 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="14" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="14" fontId="2" fillId="2" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1240,81 +1315,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="2" borderId="27" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="2" borderId="28" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="2" borderId="31" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="2" borderId="38" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="2" borderId="39" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="2" borderId="32" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1690,131 +1690,131 @@
         <v>0</v>
       </c>
       <c r="B3" s="32" t="s">
-        <v>32</v>
-      </c>
-      <c r="C3" s="49" t="s">
+        <v>31</v>
+      </c>
+      <c r="C3" s="79" t="s">
         <v>4</v>
       </c>
-      <c r="D3" s="50"/>
-      <c r="E3" s="50"/>
-      <c r="F3" s="50"/>
-      <c r="G3" s="50"/>
-      <c r="H3" s="50"/>
-      <c r="I3" s="50"/>
-      <c r="J3" s="50"/>
-      <c r="K3" s="51"/>
-      <c r="L3" s="49" t="s">
+      <c r="D3" s="80"/>
+      <c r="E3" s="80"/>
+      <c r="F3" s="80"/>
+      <c r="G3" s="80"/>
+      <c r="H3" s="80"/>
+      <c r="I3" s="80"/>
+      <c r="J3" s="80"/>
+      <c r="K3" s="81"/>
+      <c r="L3" s="79" t="s">
         <v>6</v>
       </c>
-      <c r="M3" s="50"/>
-      <c r="N3" s="50"/>
-      <c r="O3" s="50"/>
-      <c r="P3" s="50"/>
-      <c r="Q3" s="50"/>
-      <c r="R3" s="50"/>
-      <c r="S3" s="50"/>
-      <c r="T3" s="51"/>
+      <c r="M3" s="80"/>
+      <c r="N3" s="80"/>
+      <c r="O3" s="80"/>
+      <c r="P3" s="80"/>
+      <c r="Q3" s="80"/>
+      <c r="R3" s="80"/>
+      <c r="S3" s="80"/>
+      <c r="T3" s="81"/>
     </row>
     <row r="4" spans="1:20" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="52" t="s">
-        <v>42</v>
+      <c r="A4" s="77" t="s">
+        <v>41</v>
       </c>
       <c r="B4" s="27" t="s">
-        <v>31</v>
-      </c>
-      <c r="C4" s="53" t="s">
-        <v>41</v>
-      </c>
-      <c r="D4" s="54"/>
+        <v>30</v>
+      </c>
+      <c r="C4" s="75" t="s">
+        <v>40</v>
+      </c>
+      <c r="D4" s="76"/>
       <c r="E4" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F4">
         <v>5</v>
       </c>
       <c r="G4" s="39" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H4" s="41">
         <v>9</v>
       </c>
       <c r="I4" s="39" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="J4" s="41">
         <v>6.25</v>
       </c>
       <c r="K4" s="39" t="s">
+        <v>35</v>
+      </c>
+      <c r="L4" s="75" t="s">
+        <v>39</v>
+      </c>
+      <c r="M4" s="76"/>
+      <c r="N4" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="L4" s="53" t="s">
-        <v>40</v>
-      </c>
-      <c r="M4" s="54"/>
-      <c r="N4" s="7" t="s">
+      <c r="O4" s="41">
+        <v>0</v>
+      </c>
+      <c r="P4" s="39" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q4" s="41">
+        <v>0</v>
+      </c>
+      <c r="R4" s="39" t="s">
+        <v>34</v>
+      </c>
+      <c r="S4" s="41">
+        <v>0</v>
+      </c>
+      <c r="T4" s="42" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="5" spans="1:20" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="77"/>
+      <c r="B5" s="24" t="s">
+        <v>29</v>
+      </c>
+      <c r="C5" s="78">
+        <v>0</v>
+      </c>
+      <c r="D5" s="74"/>
+      <c r="E5" s="40" t="s">
+        <v>43</v>
+      </c>
+      <c r="F5" s="29"/>
+      <c r="G5" s="74">
+        <v>0</v>
+      </c>
+      <c r="H5" s="74"/>
+      <c r="I5" s="74"/>
+      <c r="J5" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="O4" s="41">
-        <v>0</v>
-      </c>
-      <c r="P4" s="39" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q4" s="41">
-        <v>0</v>
-      </c>
-      <c r="R4" s="39" t="s">
-        <v>35</v>
-      </c>
-      <c r="S4" s="41">
-        <v>0</v>
-      </c>
-      <c r="T4" s="42" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="5" spans="1:20" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="52"/>
-      <c r="B5" s="24" t="s">
-        <v>30</v>
-      </c>
-      <c r="C5" s="55">
-        <v>0</v>
-      </c>
-      <c r="D5" s="56"/>
-      <c r="E5" s="40" t="s">
-        <v>44</v>
-      </c>
-      <c r="F5" s="29"/>
-      <c r="G5" s="56">
-        <v>0</v>
-      </c>
-      <c r="H5" s="56"/>
-      <c r="I5" s="56"/>
-      <c r="J5" s="5" t="s">
-        <v>38</v>
-      </c>
       <c r="K5" s="30"/>
-      <c r="L5" s="55">
-        <v>0</v>
-      </c>
-      <c r="M5" s="56"/>
+      <c r="L5" s="78">
+        <v>0</v>
+      </c>
+      <c r="M5" s="74"/>
       <c r="N5" s="40" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="O5" s="29"/>
-      <c r="P5" s="56">
-        <v>0</v>
-      </c>
-      <c r="Q5" s="56"/>
-      <c r="R5" s="56"/>
+      <c r="P5" s="74">
+        <v>0</v>
+      </c>
+      <c r="Q5" s="74"/>
+      <c r="R5" s="74"/>
       <c r="S5" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="T5" s="30"/>
     </row>
     <row r="6" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A6" s="52"/>
+      <c r="A6" s="77"/>
       <c r="B6" s="23" t="s">
         <v>10</v>
       </c>
@@ -1822,19 +1822,19 @@
         <v>10.8</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E6" s="3">
         <v>2.1</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G6" s="3">
         <v>0.52800000000000002</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I6" s="2" t="s">
         <v>11</v>
@@ -1849,19 +1849,19 @@
         <v>144.30000000000001</v>
       </c>
       <c r="M6" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="N6" s="3">
         <v>278</v>
       </c>
       <c r="O6" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="P6" s="3">
         <v>6.97</v>
       </c>
       <c r="Q6" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="R6" s="2" t="s">
         <v>11</v>
@@ -1874,7 +1874,7 @@
       </c>
     </row>
     <row r="7" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A7" s="52"/>
+      <c r="A7" s="77"/>
       <c r="B7" s="23" t="s">
         <v>8</v>
       </c>
@@ -1882,7 +1882,7 @@
         <v>115</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I7" s="2" t="s">
         <v>11</v>
@@ -1897,7 +1897,7 @@
         <v>82.7</v>
       </c>
       <c r="M7" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="R7" s="2" t="s">
         <v>11</v>
@@ -1910,24 +1910,24 @@
       </c>
     </row>
     <row r="8" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A8" s="52"/>
+      <c r="A8" s="77"/>
       <c r="B8" s="23" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C8" s="33">
         <v>8.74</v>
       </c>
       <c r="D8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E8" s="28" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G8" s="3">
         <v>115</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I8" s="2" t="s">
         <v>11</v>
@@ -1942,16 +1942,16 @@
         <v>12.05</v>
       </c>
       <c r="M8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="N8" s="28" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="P8" s="3">
         <v>83</v>
       </c>
       <c r="Q8" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="R8" s="2" t="s">
         <v>11</v>
@@ -1964,7 +1964,7 @@
       </c>
     </row>
     <row r="9" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A9" s="52"/>
+      <c r="A9" s="77"/>
       <c r="B9" s="23" t="s">
         <v>9</v>
       </c>
@@ -1994,15 +1994,15 @@
       </c>
     </row>
     <row r="10" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A10" s="52"/>
+      <c r="A10" s="77"/>
       <c r="B10" s="24" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C10" s="34">
         <v>22.5</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E10" s="6"/>
       <c r="F10" s="5"/>
@@ -2021,7 +2021,7 @@
         <v>302.8</v>
       </c>
       <c r="M10" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="N10" s="6"/>
       <c r="O10" s="5"/>
@@ -2038,105 +2038,105 @@
       </c>
     </row>
     <row r="11" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="52" t="s">
-        <v>45</v>
+      <c r="A11" s="77" t="s">
+        <v>44</v>
       </c>
       <c r="B11" s="27" t="s">
-        <v>31</v>
-      </c>
-      <c r="C11" s="53" t="s">
-        <v>41</v>
-      </c>
-      <c r="D11" s="54"/>
+        <v>30</v>
+      </c>
+      <c r="C11" s="75" t="s">
+        <v>40</v>
+      </c>
+      <c r="D11" s="76"/>
       <c r="E11" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F11">
         <v>5</v>
       </c>
       <c r="G11" s="39" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H11" s="41">
         <v>9</v>
       </c>
       <c r="I11" s="39" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="J11" s="41">
         <v>6.25</v>
       </c>
       <c r="K11" s="39" t="s">
+        <v>35</v>
+      </c>
+      <c r="L11" s="75" t="s">
+        <v>39</v>
+      </c>
+      <c r="M11" s="76"/>
+      <c r="N11" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="L11" s="53" t="s">
-        <v>40</v>
-      </c>
-      <c r="M11" s="54"/>
-      <c r="N11" s="7" t="s">
+      <c r="O11" s="41">
+        <v>0</v>
+      </c>
+      <c r="P11" s="39" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q11" s="41">
+        <v>0</v>
+      </c>
+      <c r="R11" s="39" t="s">
+        <v>34</v>
+      </c>
+      <c r="S11" s="41">
+        <v>0</v>
+      </c>
+      <c r="T11" s="42" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="12" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A12" s="77"/>
+      <c r="B12" s="24" t="s">
+        <v>29</v>
+      </c>
+      <c r="C12" s="78">
+        <v>0</v>
+      </c>
+      <c r="D12" s="74"/>
+      <c r="E12" s="40" t="s">
+        <v>43</v>
+      </c>
+      <c r="F12" s="29"/>
+      <c r="G12" s="74">
+        <v>0</v>
+      </c>
+      <c r="H12" s="74"/>
+      <c r="I12" s="74"/>
+      <c r="J12" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="O11" s="41">
-        <v>0</v>
-      </c>
-      <c r="P11" s="39" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q11" s="41">
-        <v>0</v>
-      </c>
-      <c r="R11" s="39" t="s">
-        <v>35</v>
-      </c>
-      <c r="S11" s="41">
-        <v>0</v>
-      </c>
-      <c r="T11" s="42" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A12" s="52"/>
-      <c r="B12" s="24" t="s">
-        <v>30</v>
-      </c>
-      <c r="C12" s="55">
-        <v>0</v>
-      </c>
-      <c r="D12" s="56"/>
-      <c r="E12" s="40" t="s">
-        <v>44</v>
-      </c>
-      <c r="F12" s="29"/>
-      <c r="G12" s="56">
-        <v>0</v>
-      </c>
-      <c r="H12" s="56"/>
-      <c r="I12" s="56"/>
-      <c r="J12" s="5" t="s">
-        <v>38</v>
-      </c>
       <c r="K12" s="30"/>
-      <c r="L12" s="55">
-        <v>0</v>
-      </c>
-      <c r="M12" s="56"/>
+      <c r="L12" s="78">
+        <v>0</v>
+      </c>
+      <c r="M12" s="74"/>
       <c r="N12" s="40" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="O12" s="29"/>
-      <c r="P12" s="56">
-        <v>0</v>
-      </c>
-      <c r="Q12" s="56"/>
-      <c r="R12" s="56"/>
+      <c r="P12" s="74">
+        <v>0</v>
+      </c>
+      <c r="Q12" s="74"/>
+      <c r="R12" s="74"/>
       <c r="S12" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="T12" s="30"/>
     </row>
     <row r="13" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A13" s="52"/>
+      <c r="A13" s="77"/>
       <c r="B13" s="23" t="s">
         <v>10</v>
       </c>
@@ -2144,19 +2144,19 @@
         <v>74.7</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E13" s="3">
         <v>147.1</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G13" s="3">
         <v>6.05</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I13" s="2" t="s">
         <v>11</v>
@@ -2171,19 +2171,19 @@
         <v>120.5</v>
       </c>
       <c r="M13" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="N13" s="3">
         <v>237</v>
       </c>
       <c r="O13" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="P13" s="3">
         <v>9.2100000000000009</v>
       </c>
       <c r="Q13" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="R13" s="2" t="s">
         <v>11</v>
@@ -2196,7 +2196,7 @@
       </c>
     </row>
     <row r="14" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A14" s="52"/>
+      <c r="A14" s="77"/>
       <c r="B14" s="23" t="s">
         <v>8</v>
       </c>
@@ -2204,7 +2204,7 @@
         <v>151.1</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I14" s="2" t="s">
         <v>11</v>
@@ -2219,7 +2219,7 @@
         <v>51</v>
       </c>
       <c r="M14" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="R14" s="2" t="s">
         <v>11</v>
@@ -2232,24 +2232,24 @@
       </c>
     </row>
     <row r="15" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A15" s="52"/>
+      <c r="A15" s="77"/>
       <c r="B15" s="23" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C15" s="33">
         <v>6.62</v>
       </c>
       <c r="D15" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E15" s="28" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G15" s="3">
         <v>151</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I15" s="2" t="s">
         <v>11</v>
@@ -2264,16 +2264,16 @@
         <v>19.2</v>
       </c>
       <c r="M15" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="N15" s="28" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="P15" s="3">
         <v>52</v>
       </c>
       <c r="Q15" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="R15" s="2" t="s">
         <v>11</v>
@@ -2286,7 +2286,7 @@
       </c>
     </row>
     <row r="16" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A16" s="52"/>
+      <c r="A16" s="77"/>
       <c r="B16" s="23" t="s">
         <v>9</v>
       </c>
@@ -2316,15 +2316,15 @@
       </c>
     </row>
     <row r="17" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A17" s="52"/>
+      <c r="A17" s="77"/>
       <c r="B17" s="24" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C17" s="34">
         <v>217.8</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E17" s="6"/>
       <c r="F17" s="5"/>
@@ -2343,7 +2343,7 @@
         <v>299.3</v>
       </c>
       <c r="M17" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="N17" s="6"/>
       <c r="O17" s="5"/>
@@ -2360,105 +2360,105 @@
       </c>
     </row>
     <row r="18" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="52" t="s">
-        <v>56</v>
+      <c r="A18" s="77" t="s">
+        <v>55</v>
       </c>
       <c r="B18" s="27" t="s">
-        <v>31</v>
-      </c>
-      <c r="C18" s="53" t="s">
-        <v>41</v>
-      </c>
-      <c r="D18" s="54"/>
+        <v>30</v>
+      </c>
+      <c r="C18" s="75" t="s">
+        <v>40</v>
+      </c>
+      <c r="D18" s="76"/>
       <c r="E18" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F18">
         <v>5</v>
       </c>
       <c r="G18" s="39" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H18" s="41">
         <v>9</v>
       </c>
       <c r="I18" s="39" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="J18" s="41">
         <v>6.25</v>
       </c>
       <c r="K18" s="39" t="s">
+        <v>35</v>
+      </c>
+      <c r="L18" s="75" t="s">
+        <v>40</v>
+      </c>
+      <c r="M18" s="76"/>
+      <c r="N18" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="L18" s="53" t="s">
-        <v>41</v>
-      </c>
-      <c r="M18" s="54"/>
-      <c r="N18" s="7" t="s">
-        <v>37</v>
-      </c>
       <c r="O18" s="41">
         <v>5</v>
       </c>
       <c r="P18" s="39" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="Q18" s="41">
         <v>9</v>
       </c>
       <c r="R18" s="39" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="S18" s="41">
         <v>6.25</v>
       </c>
       <c r="T18" s="42" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="19" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A19" s="52"/>
+      <c r="A19" s="77"/>
       <c r="B19" s="24" t="s">
-        <v>30</v>
-      </c>
-      <c r="C19" s="55">
-        <v>0</v>
-      </c>
-      <c r="D19" s="56"/>
+        <v>29</v>
+      </c>
+      <c r="C19" s="78">
+        <v>0</v>
+      </c>
+      <c r="D19" s="74"/>
       <c r="E19" s="40" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F19" s="29"/>
-      <c r="G19" s="56">
-        <v>0</v>
-      </c>
-      <c r="H19" s="56"/>
-      <c r="I19" s="56"/>
+      <c r="G19" s="74">
+        <v>0</v>
+      </c>
+      <c r="H19" s="74"/>
+      <c r="I19" s="74"/>
       <c r="J19" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="K19" s="30"/>
-      <c r="L19" s="55">
-        <v>0</v>
-      </c>
-      <c r="M19" s="56"/>
+      <c r="L19" s="78">
+        <v>0</v>
+      </c>
+      <c r="M19" s="74"/>
       <c r="N19" s="40" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="O19" s="29"/>
-      <c r="P19" s="56">
-        <v>0</v>
-      </c>
-      <c r="Q19" s="56"/>
-      <c r="R19" s="56"/>
+      <c r="P19" s="74">
+        <v>0</v>
+      </c>
+      <c r="Q19" s="74"/>
+      <c r="R19" s="74"/>
       <c r="S19" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="T19" s="30"/>
     </row>
     <row r="20" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A20" s="52"/>
+      <c r="A20" s="77"/>
       <c r="B20" s="23" t="s">
         <v>10</v>
       </c>
@@ -2466,19 +2466,19 @@
         <v>82.2</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E20" s="3">
         <v>164</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G20" s="3">
         <v>5.2</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I20" s="2" t="s">
         <v>11</v>
@@ -2493,19 +2493,19 @@
         <v>60</v>
       </c>
       <c r="M20" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="N20" s="3">
         <v>119.6</v>
       </c>
       <c r="O20" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="P20" s="3">
         <v>4</v>
       </c>
       <c r="Q20" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="R20" s="2" t="s">
         <v>11</v>
@@ -2518,7 +2518,7 @@
       </c>
     </row>
     <row r="21" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A21" s="52"/>
+      <c r="A21" s="77"/>
       <c r="B21" s="23" t="s">
         <v>8</v>
       </c>
@@ -2526,7 +2526,7 @@
         <v>236</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I21" s="2" t="s">
         <v>11</v>
@@ -2541,7 +2541,7 @@
         <v>141.69999999999999</v>
       </c>
       <c r="M21" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="R21" s="2" t="s">
         <v>11</v>
@@ -2554,24 +2554,24 @@
       </c>
     </row>
     <row r="22" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A22" s="52"/>
+      <c r="A22" s="77"/>
       <c r="B22" s="23" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C22" s="33">
         <v>4.24</v>
       </c>
       <c r="D22" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E22" s="28" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G22" s="3">
         <v>236</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I22" s="2" t="s">
         <v>11</v>
@@ -2586,16 +2586,16 @@
         <v>7.09</v>
       </c>
       <c r="M22" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="N22" s="28" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="P22" s="3">
         <v>141</v>
       </c>
       <c r="Q22" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="R22" s="2" t="s">
         <v>11</v>
@@ -2608,7 +2608,7 @@
       </c>
     </row>
     <row r="23" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A23" s="52"/>
+      <c r="A23" s="77"/>
       <c r="B23" s="23" t="s">
         <v>9</v>
       </c>
@@ -2638,15 +2638,15 @@
       </c>
     </row>
     <row r="24" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A24" s="52"/>
+      <c r="A24" s="77"/>
       <c r="B24" s="24" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C24" s="34">
         <v>117.9</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E24" s="6"/>
       <c r="F24" s="5"/>
@@ -2665,7 +2665,7 @@
         <v>281</v>
       </c>
       <c r="M24" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="N24" s="6"/>
       <c r="O24" s="5"/>
@@ -2682,105 +2682,105 @@
       </c>
     </row>
     <row r="25" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A25" s="52" t="s">
-        <v>62</v>
+      <c r="A25" s="77" t="s">
+        <v>61</v>
       </c>
       <c r="B25" s="27" t="s">
-        <v>31</v>
-      </c>
-      <c r="C25" s="53" t="s">
-        <v>41</v>
-      </c>
-      <c r="D25" s="54"/>
+        <v>30</v>
+      </c>
+      <c r="C25" s="75" t="s">
+        <v>40</v>
+      </c>
+      <c r="D25" s="76"/>
       <c r="E25" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F25">
         <v>5</v>
       </c>
       <c r="G25" s="39" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H25" s="41">
         <v>9</v>
       </c>
       <c r="I25" s="39" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="J25" s="41">
         <v>6.25</v>
       </c>
       <c r="K25" s="39" t="s">
+        <v>35</v>
+      </c>
+      <c r="L25" s="75" t="s">
+        <v>39</v>
+      </c>
+      <c r="M25" s="76"/>
+      <c r="N25" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="L25" s="53" t="s">
-        <v>40</v>
-      </c>
-      <c r="M25" s="54"/>
-      <c r="N25" s="7" t="s">
+      <c r="O25" s="41">
+        <v>0</v>
+      </c>
+      <c r="P25" s="39" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q25" s="41">
+        <v>0</v>
+      </c>
+      <c r="R25" s="39" t="s">
+        <v>34</v>
+      </c>
+      <c r="S25" s="41">
+        <v>0</v>
+      </c>
+      <c r="T25" s="42" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="26" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A26" s="77"/>
+      <c r="B26" s="24" t="s">
+        <v>29</v>
+      </c>
+      <c r="C26" s="78">
+        <v>0</v>
+      </c>
+      <c r="D26" s="74"/>
+      <c r="E26" s="40" t="s">
         <v>37</v>
       </c>
-      <c r="O25" s="41">
-        <v>0</v>
-      </c>
-      <c r="P25" s="39" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q25" s="41">
-        <v>0</v>
-      </c>
-      <c r="R25" s="39" t="s">
-        <v>35</v>
-      </c>
-      <c r="S25" s="41">
-        <v>0</v>
-      </c>
-      <c r="T25" s="42" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="26" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A26" s="52"/>
-      <c r="B26" s="24" t="s">
-        <v>30</v>
-      </c>
-      <c r="C26" s="55">
-        <v>0</v>
-      </c>
-      <c r="D26" s="56"/>
-      <c r="E26" s="40" t="s">
-        <v>38</v>
-      </c>
       <c r="F26" s="29"/>
-      <c r="G26" s="56">
-        <v>0</v>
-      </c>
-      <c r="H26" s="56"/>
-      <c r="I26" s="56"/>
+      <c r="G26" s="74">
+        <v>0</v>
+      </c>
+      <c r="H26" s="74"/>
+      <c r="I26" s="74"/>
       <c r="J26" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="K26" s="30"/>
-      <c r="L26" s="55">
-        <v>0</v>
-      </c>
-      <c r="M26" s="56"/>
+      <c r="L26" s="78">
+        <v>0</v>
+      </c>
+      <c r="M26" s="74"/>
       <c r="N26" s="40" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="O26" s="29"/>
-      <c r="P26" s="56">
-        <v>0</v>
-      </c>
-      <c r="Q26" s="56"/>
-      <c r="R26" s="56"/>
+      <c r="P26" s="74">
+        <v>0</v>
+      </c>
+      <c r="Q26" s="74"/>
+      <c r="R26" s="74"/>
       <c r="S26" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="T26" s="30"/>
     </row>
     <row r="27" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A27" s="52"/>
+      <c r="A27" s="77"/>
       <c r="B27" s="23" t="s">
         <v>10</v>
       </c>
@@ -2788,19 +2788,19 @@
         <v>114.9</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E27" s="3">
         <v>233</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G27" s="3">
         <v>8.07</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I27" s="2" t="s">
         <v>11</v>
@@ -2815,19 +2815,19 @@
         <v>81.400000000000006</v>
       </c>
       <c r="M27" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="N27" s="3">
         <v>164.8</v>
       </c>
       <c r="O27" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="P27" s="3">
         <v>5.99</v>
       </c>
       <c r="Q27" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="R27" s="2" t="s">
         <v>11</v>
@@ -2840,7 +2840,7 @@
       </c>
     </row>
     <row r="28" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A28" s="52"/>
+      <c r="A28" s="77"/>
       <c r="B28" s="23" t="s">
         <v>8</v>
       </c>
@@ -2848,7 +2848,7 @@
         <v>265</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I28" s="2" t="s">
         <v>11</v>
@@ -2863,7 +2863,7 @@
         <v>70.2</v>
       </c>
       <c r="M28" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="R28" s="2" t="s">
         <v>11</v>
@@ -2876,24 +2876,24 @@
       </c>
     </row>
     <row r="29" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A29" s="52"/>
+      <c r="A29" s="77"/>
       <c r="B29" s="23" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C29" s="33">
         <v>3.77</v>
       </c>
       <c r="D29" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E29" s="28" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G29" s="3">
         <v>265</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I29" s="2" t="s">
         <v>11</v>
@@ -2908,16 +2908,16 @@
         <v>14.25</v>
       </c>
       <c r="M29" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="N29" s="28" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="P29" s="3">
         <v>70</v>
       </c>
       <c r="Q29" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="R29" s="2" t="s">
         <v>11</v>
@@ -2930,7 +2930,7 @@
       </c>
     </row>
     <row r="30" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A30" s="52"/>
+      <c r="A30" s="77"/>
       <c r="B30" s="23" t="s">
         <v>9</v>
       </c>
@@ -2960,15 +2960,15 @@
       </c>
     </row>
     <row r="31" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A31" s="52"/>
+      <c r="A31" s="77"/>
       <c r="B31" s="24" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C31" s="34">
         <v>216.2</v>
       </c>
       <c r="D31" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E31" s="6"/>
       <c r="F31" s="5"/>
@@ -2987,7 +2987,7 @@
         <v>332.4</v>
       </c>
       <c r="M31" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="N31" s="6"/>
       <c r="O31" s="5"/>
@@ -3005,25 +3005,11 @@
     </row>
     <row r="33" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C33" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="30">
-    <mergeCell ref="P12:R12"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="A18:A24"/>
-    <mergeCell ref="P26:R26"/>
-    <mergeCell ref="L18:M18"/>
-    <mergeCell ref="L19:M19"/>
-    <mergeCell ref="P19:R19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="G19:I19"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="L25:M25"/>
-    <mergeCell ref="L26:M26"/>
-    <mergeCell ref="C26:D26"/>
-    <mergeCell ref="G26:I26"/>
     <mergeCell ref="C3:K3"/>
     <mergeCell ref="L3:T3"/>
     <mergeCell ref="A25:A31"/>
@@ -3040,6 +3026,20 @@
     <mergeCell ref="L12:M12"/>
     <mergeCell ref="A4:A10"/>
     <mergeCell ref="A11:A17"/>
+    <mergeCell ref="P12:R12"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="A18:A24"/>
+    <mergeCell ref="P26:R26"/>
+    <mergeCell ref="L18:M18"/>
+    <mergeCell ref="L19:M19"/>
+    <mergeCell ref="P19:R19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="G19:I19"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="L25:M25"/>
+    <mergeCell ref="L26:M26"/>
+    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="G26:I26"/>
   </mergeCells>
   <pageMargins left="0.19685039370078741" right="0.11811023622047245" top="0.78740157480314965" bottom="0.78740157480314965" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>
@@ -3106,200 +3106,200 @@
         <v>0</v>
       </c>
       <c r="B3" s="32" t="s">
-        <v>32</v>
-      </c>
-      <c r="C3" s="49" t="s">
+        <v>31</v>
+      </c>
+      <c r="C3" s="79" t="s">
         <v>4</v>
       </c>
-      <c r="D3" s="50"/>
-      <c r="E3" s="50"/>
-      <c r="F3" s="50"/>
-      <c r="G3" s="50"/>
-      <c r="H3" s="50"/>
-      <c r="I3" s="50"/>
-      <c r="J3" s="50"/>
-      <c r="K3" s="51"/>
-      <c r="L3" s="49" t="s">
+      <c r="D3" s="80"/>
+      <c r="E3" s="80"/>
+      <c r="F3" s="80"/>
+      <c r="G3" s="80"/>
+      <c r="H3" s="80"/>
+      <c r="I3" s="80"/>
+      <c r="J3" s="80"/>
+      <c r="K3" s="81"/>
+      <c r="L3" s="79" t="s">
         <v>6</v>
       </c>
-      <c r="M3" s="50"/>
-      <c r="N3" s="50"/>
-      <c r="O3" s="50"/>
-      <c r="P3" s="50"/>
-      <c r="Q3" s="50"/>
-      <c r="R3" s="50"/>
-      <c r="S3" s="50"/>
-      <c r="T3" s="51"/>
+      <c r="M3" s="80"/>
+      <c r="N3" s="80"/>
+      <c r="O3" s="80"/>
+      <c r="P3" s="80"/>
+      <c r="Q3" s="80"/>
+      <c r="R3" s="80"/>
+      <c r="S3" s="80"/>
+      <c r="T3" s="81"/>
       <c r="U3" s="31" t="s">
         <v>0</v>
       </c>
       <c r="V3" s="32" t="s">
-        <v>32</v>
-      </c>
-      <c r="W3" s="49" t="s">
+        <v>31</v>
+      </c>
+      <c r="W3" s="79" t="s">
         <v>7</v>
       </c>
-      <c r="X3" s="50"/>
-      <c r="Y3" s="50"/>
-      <c r="Z3" s="50"/>
-      <c r="AA3" s="50"/>
-      <c r="AB3" s="50"/>
-      <c r="AC3" s="50"/>
-      <c r="AD3" s="50"/>
-      <c r="AE3" s="51"/>
+      <c r="X3" s="80"/>
+      <c r="Y3" s="80"/>
+      <c r="Z3" s="80"/>
+      <c r="AA3" s="80"/>
+      <c r="AB3" s="80"/>
+      <c r="AC3" s="80"/>
+      <c r="AD3" s="80"/>
+      <c r="AE3" s="81"/>
     </row>
     <row r="4" spans="1:32" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="52" t="s">
-        <v>42</v>
+      <c r="A4" s="77" t="s">
+        <v>41</v>
       </c>
       <c r="B4" s="27" t="s">
-        <v>31</v>
-      </c>
-      <c r="C4" s="53" t="s">
-        <v>40</v>
-      </c>
-      <c r="D4" s="54"/>
+        <v>30</v>
+      </c>
+      <c r="C4" s="75" t="s">
+        <v>39</v>
+      </c>
+      <c r="D4" s="76"/>
       <c r="E4" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="F4">
+        <v>0</v>
+      </c>
+      <c r="G4" s="39" t="s">
+        <v>33</v>
+      </c>
+      <c r="H4" s="41">
+        <v>0</v>
+      </c>
+      <c r="I4" s="39" t="s">
+        <v>34</v>
+      </c>
+      <c r="J4" s="41">
+        <v>0</v>
+      </c>
+      <c r="K4" s="39" t="s">
+        <v>35</v>
+      </c>
+      <c r="L4" s="75" t="s">
+        <v>39</v>
+      </c>
+      <c r="M4" s="76"/>
+      <c r="N4" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="O4">
+        <v>0</v>
+      </c>
+      <c r="P4" s="39" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q4" s="41">
+        <v>0</v>
+      </c>
+      <c r="R4" s="39" t="s">
+        <v>34</v>
+      </c>
+      <c r="S4" s="41">
+        <v>0</v>
+      </c>
+      <c r="T4" s="39" t="s">
+        <v>35</v>
+      </c>
+      <c r="U4" s="77" t="s">
+        <v>41</v>
+      </c>
+      <c r="V4" s="27" t="s">
+        <v>30</v>
+      </c>
+      <c r="W4" s="75" t="s">
+        <v>39</v>
+      </c>
+      <c r="X4" s="76"/>
+      <c r="Y4" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="Z4" s="41">
+        <v>0</v>
+      </c>
+      <c r="AA4" s="39" t="s">
+        <v>33</v>
+      </c>
+      <c r="AB4" s="41">
+        <v>0</v>
+      </c>
+      <c r="AC4" s="39" t="s">
+        <v>34</v>
+      </c>
+      <c r="AD4" s="41">
+        <v>0</v>
+      </c>
+      <c r="AE4" s="42" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="5" spans="1:32" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="77"/>
+      <c r="B5" s="24" t="s">
+        <v>29</v>
+      </c>
+      <c r="C5" s="78">
+        <v>0</v>
+      </c>
+      <c r="D5" s="74"/>
+      <c r="E5" s="40" t="s">
+        <v>43</v>
+      </c>
+      <c r="F5" s="29"/>
+      <c r="G5" s="74">
+        <v>0</v>
+      </c>
+      <c r="H5" s="74"/>
+      <c r="I5" s="74"/>
+      <c r="J5" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="F4">
-        <v>0</v>
-      </c>
-      <c r="G4" s="39" t="s">
-        <v>34</v>
-      </c>
-      <c r="H4" s="41">
-        <v>0</v>
-      </c>
-      <c r="I4" s="39" t="s">
-        <v>35</v>
-      </c>
-      <c r="J4" s="41">
-        <v>0</v>
-      </c>
-      <c r="K4" s="39" t="s">
-        <v>36</v>
-      </c>
-      <c r="L4" s="53" t="s">
-        <v>40</v>
-      </c>
-      <c r="M4" s="54"/>
-      <c r="N4" s="2" t="s">
+      <c r="K5" s="30"/>
+      <c r="L5" s="78">
+        <v>0</v>
+      </c>
+      <c r="M5" s="74"/>
+      <c r="N5" s="40" t="s">
+        <v>43</v>
+      </c>
+      <c r="O5" s="29"/>
+      <c r="P5" s="74">
+        <v>0</v>
+      </c>
+      <c r="Q5" s="74"/>
+      <c r="R5" s="74"/>
+      <c r="S5" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="O4">
-        <v>0</v>
-      </c>
-      <c r="P4" s="39" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q4" s="41">
-        <v>0</v>
-      </c>
-      <c r="R4" s="39" t="s">
-        <v>35</v>
-      </c>
-      <c r="S4" s="41">
-        <v>0</v>
-      </c>
-      <c r="T4" s="39" t="s">
-        <v>36</v>
-      </c>
-      <c r="U4" s="52" t="s">
-        <v>42</v>
-      </c>
-      <c r="V4" s="27" t="s">
-        <v>31</v>
-      </c>
-      <c r="W4" s="53" t="s">
-        <v>40</v>
-      </c>
-      <c r="X4" s="54"/>
-      <c r="Y4" s="7" t="s">
+      <c r="T5" s="30"/>
+      <c r="U5" s="77"/>
+      <c r="V5" s="24" t="s">
+        <v>29</v>
+      </c>
+      <c r="W5" s="78">
+        <v>0</v>
+      </c>
+      <c r="X5" s="74"/>
+      <c r="Y5" s="40" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z5" s="29"/>
+      <c r="AA5" s="74">
+        <v>0</v>
+      </c>
+      <c r="AB5" s="74"/>
+      <c r="AC5" s="74"/>
+      <c r="AD5" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="Z4" s="41">
-        <v>0</v>
-      </c>
-      <c r="AA4" s="39" t="s">
-        <v>34</v>
-      </c>
-      <c r="AB4" s="41">
-        <v>0</v>
-      </c>
-      <c r="AC4" s="39" t="s">
-        <v>35</v>
-      </c>
-      <c r="AD4" s="41">
-        <v>0</v>
-      </c>
-      <c r="AE4" s="42" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="5" spans="1:32" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="52"/>
-      <c r="B5" s="24" t="s">
-        <v>30</v>
-      </c>
-      <c r="C5" s="55">
-        <v>0</v>
-      </c>
-      <c r="D5" s="56"/>
-      <c r="E5" s="40" t="s">
-        <v>44</v>
-      </c>
-      <c r="F5" s="29"/>
-      <c r="G5" s="56">
-        <v>0</v>
-      </c>
-      <c r="H5" s="56"/>
-      <c r="I5" s="56"/>
-      <c r="J5" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="K5" s="30"/>
-      <c r="L5" s="55">
-        <v>0</v>
-      </c>
-      <c r="M5" s="56"/>
-      <c r="N5" s="40" t="s">
-        <v>44</v>
-      </c>
-      <c r="O5" s="29"/>
-      <c r="P5" s="56">
-        <v>0</v>
-      </c>
-      <c r="Q5" s="56"/>
-      <c r="R5" s="56"/>
-      <c r="S5" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="T5" s="30"/>
-      <c r="U5" s="52"/>
-      <c r="V5" s="24" t="s">
-        <v>30</v>
-      </c>
-      <c r="W5" s="55">
-        <v>0</v>
-      </c>
-      <c r="X5" s="56"/>
-      <c r="Y5" s="40" t="s">
-        <v>44</v>
-      </c>
-      <c r="Z5" s="29"/>
-      <c r="AA5" s="56">
-        <v>0</v>
-      </c>
-      <c r="AB5" s="56"/>
-      <c r="AC5" s="56"/>
-      <c r="AD5" s="5" t="s">
-        <v>38</v>
-      </c>
       <c r="AE5" s="30"/>
     </row>
     <row r="6" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A6" s="52"/>
+      <c r="A6" s="77"/>
       <c r="B6" s="23" t="s">
         <v>10</v>
       </c>
@@ -3307,19 +3307,19 @@
         <v>29.2</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E6" s="1">
         <v>58.2</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G6" s="1">
         <v>1.71</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I6" s="2" t="s">
         <v>11</v>
@@ -3334,19 +3334,19 @@
         <v>13</v>
       </c>
       <c r="M6" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="N6" s="1">
         <v>25.9</v>
       </c>
       <c r="O6" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="P6" s="1">
         <v>0.7</v>
       </c>
       <c r="Q6" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="R6" s="2" t="s">
         <v>11</v>
@@ -3357,7 +3357,7 @@
       <c r="T6" s="21" t="s">
         <v>5</v>
       </c>
-      <c r="U6" s="52"/>
+      <c r="U6" s="77"/>
       <c r="V6" s="23" t="s">
         <v>10</v>
       </c>
@@ -3365,19 +3365,19 @@
         <v>27.5</v>
       </c>
       <c r="X6" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="Y6" s="3">
         <v>54.7</v>
       </c>
       <c r="Z6" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AA6" s="1">
         <v>1.6</v>
       </c>
       <c r="AB6" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AC6" s="2" t="s">
         <v>11</v>
@@ -3390,7 +3390,7 @@
       </c>
     </row>
     <row r="7" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A7" s="52"/>
+      <c r="A7" s="77"/>
       <c r="B7" s="23" t="s">
         <v>8</v>
       </c>
@@ -3398,7 +3398,7 @@
         <v>27.3</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I7" s="2" t="s">
         <v>11</v>
@@ -3413,7 +3413,7 @@
         <v>34.6</v>
       </c>
       <c r="M7" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="R7" s="2" t="s">
         <v>11</v>
@@ -3424,7 +3424,7 @@
       <c r="T7" s="21" t="s">
         <v>5</v>
       </c>
-      <c r="U7" s="52"/>
+      <c r="U7" s="77"/>
       <c r="V7" s="23" t="s">
         <v>8</v>
       </c>
@@ -3432,7 +3432,7 @@
         <v>25.6</v>
       </c>
       <c r="X7" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AC7" s="2" t="s">
         <v>11</v>
@@ -3445,24 +3445,24 @@
       </c>
     </row>
     <row r="8" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A8" s="52"/>
+      <c r="A8" s="77"/>
       <c r="B8" s="23" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C8" s="36">
         <v>36.4</v>
       </c>
       <c r="D8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E8" s="28" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G8" s="1">
         <v>27</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I8" s="2" t="s">
         <v>11</v>
@@ -3477,16 +3477,16 @@
         <v>29.2</v>
       </c>
       <c r="M8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="N8" s="28" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="P8" s="1">
         <v>34</v>
       </c>
       <c r="Q8" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="R8" s="2" t="s">
         <v>11</v>
@@ -3497,24 +3497,24 @@
       <c r="T8" s="21" t="s">
         <v>5</v>
       </c>
-      <c r="U8" s="52"/>
+      <c r="U8" s="77"/>
       <c r="V8" s="23" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="W8" s="36">
         <v>39.5</v>
       </c>
       <c r="X8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y8" s="28" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AA8" s="1">
         <v>25</v>
       </c>
       <c r="AB8" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AC8" s="2" t="s">
         <v>11</v>
@@ -3527,7 +3527,7 @@
       </c>
     </row>
     <row r="9" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A9" s="52"/>
+      <c r="A9" s="77"/>
       <c r="B9" s="23" t="s">
         <v>9</v>
       </c>
@@ -3555,7 +3555,7 @@
       <c r="T9" s="21" t="s">
         <v>5</v>
       </c>
-      <c r="U9" s="52"/>
+      <c r="U9" s="77"/>
       <c r="V9" s="23" t="s">
         <v>9</v>
       </c>
@@ -3573,15 +3573,15 @@
       </c>
     </row>
     <row r="10" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A10" s="52"/>
+      <c r="A10" s="77"/>
       <c r="B10" s="24" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C10" s="37">
         <v>245.2</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E10" s="6"/>
       <c r="F10" s="5"/>
@@ -3600,7 +3600,7 @@
         <v>282</v>
       </c>
       <c r="M10" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="N10" s="6"/>
       <c r="O10" s="5"/>
@@ -3615,15 +3615,15 @@
       <c r="T10" s="22" t="s">
         <v>5</v>
       </c>
-      <c r="U10" s="52"/>
+      <c r="U10" s="77"/>
       <c r="V10" s="24" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="W10" s="37">
         <v>299</v>
       </c>
       <c r="X10" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Y10" s="6"/>
       <c r="Z10" s="5"/>
@@ -3640,160 +3640,160 @@
       </c>
     </row>
     <row r="11" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="52" t="s">
+      <c r="A11" s="77" t="s">
+        <v>44</v>
+      </c>
+      <c r="B11" s="27" t="s">
+        <v>30</v>
+      </c>
+      <c r="C11" s="75" t="s">
+        <v>39</v>
+      </c>
+      <c r="D11" s="76"/>
+      <c r="E11" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="F11" s="41">
+        <v>0</v>
+      </c>
+      <c r="G11" s="39" t="s">
+        <v>33</v>
+      </c>
+      <c r="H11" s="41">
+        <v>0</v>
+      </c>
+      <c r="I11" s="39" t="s">
+        <v>34</v>
+      </c>
+      <c r="J11" s="41">
+        <v>0</v>
+      </c>
+      <c r="K11" s="39" t="s">
+        <v>35</v>
+      </c>
+      <c r="L11" s="75" t="s">
+        <v>39</v>
+      </c>
+      <c r="M11" s="76"/>
+      <c r="N11" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="O11" s="41">
+        <v>0</v>
+      </c>
+      <c r="P11" s="39" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q11" s="41">
+        <v>0</v>
+      </c>
+      <c r="R11" s="39" t="s">
+        <v>34</v>
+      </c>
+      <c r="S11" s="41">
+        <v>0</v>
+      </c>
+      <c r="T11" s="39" t="s">
+        <v>35</v>
+      </c>
+      <c r="U11" s="77" t="s">
+        <v>44</v>
+      </c>
+      <c r="V11" s="27" t="s">
+        <v>30</v>
+      </c>
+      <c r="W11" s="75" t="s">
+        <v>39</v>
+      </c>
+      <c r="X11" s="76"/>
+      <c r="Y11" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="Z11" s="41">
+        <v>0</v>
+      </c>
+      <c r="AA11" s="39" t="s">
+        <v>33</v>
+      </c>
+      <c r="AB11" s="41">
+        <v>0</v>
+      </c>
+      <c r="AC11" s="39" t="s">
+        <v>34</v>
+      </c>
+      <c r="AD11" s="41">
+        <v>0</v>
+      </c>
+      <c r="AE11" s="42" t="s">
+        <v>35</v>
+      </c>
+      <c r="AF11" t="s">
         <v>45</v>
       </c>
-      <c r="B11" s="27" t="s">
-        <v>31</v>
-      </c>
-      <c r="C11" s="53" t="s">
-        <v>40</v>
-      </c>
-      <c r="D11" s="54"/>
-      <c r="E11" s="7" t="s">
+    </row>
+    <row r="12" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="A12" s="77"/>
+      <c r="B12" s="24" t="s">
+        <v>29</v>
+      </c>
+      <c r="C12" s="78">
+        <v>0</v>
+      </c>
+      <c r="D12" s="74"/>
+      <c r="E12" s="40" t="s">
+        <v>43</v>
+      </c>
+      <c r="F12" s="29"/>
+      <c r="G12" s="74">
+        <v>0</v>
+      </c>
+      <c r="H12" s="74"/>
+      <c r="I12" s="74"/>
+      <c r="J12" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="F11" s="41">
-        <v>0</v>
-      </c>
-      <c r="G11" s="39" t="s">
-        <v>34</v>
-      </c>
-      <c r="H11" s="41">
-        <v>0</v>
-      </c>
-      <c r="I11" s="39" t="s">
-        <v>35</v>
-      </c>
-      <c r="J11" s="41">
-        <v>0</v>
-      </c>
-      <c r="K11" s="39" t="s">
-        <v>36</v>
-      </c>
-      <c r="L11" s="53" t="s">
-        <v>40</v>
-      </c>
-      <c r="M11" s="54"/>
-      <c r="N11" s="7" t="s">
+      <c r="K12" s="30"/>
+      <c r="L12" s="78">
+        <v>0</v>
+      </c>
+      <c r="M12" s="74"/>
+      <c r="N12" s="40" t="s">
+        <v>43</v>
+      </c>
+      <c r="O12" s="29"/>
+      <c r="P12" s="74">
+        <v>0</v>
+      </c>
+      <c r="Q12" s="74"/>
+      <c r="R12" s="74"/>
+      <c r="S12" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="O11" s="41">
-        <v>0</v>
-      </c>
-      <c r="P11" s="39" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q11" s="41">
-        <v>0</v>
-      </c>
-      <c r="R11" s="39" t="s">
-        <v>35</v>
-      </c>
-      <c r="S11" s="41">
-        <v>0</v>
-      </c>
-      <c r="T11" s="39" t="s">
-        <v>36</v>
-      </c>
-      <c r="U11" s="52" t="s">
-        <v>45</v>
-      </c>
-      <c r="V11" s="27" t="s">
-        <v>31</v>
-      </c>
-      <c r="W11" s="53" t="s">
-        <v>40</v>
-      </c>
-      <c r="X11" s="54"/>
-      <c r="Y11" s="7" t="s">
+      <c r="T12" s="30"/>
+      <c r="U12" s="77"/>
+      <c r="V12" s="24" t="s">
+        <v>29</v>
+      </c>
+      <c r="W12" s="78">
+        <v>0</v>
+      </c>
+      <c r="X12" s="74"/>
+      <c r="Y12" s="40" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z12" s="29"/>
+      <c r="AA12" s="74">
+        <v>0</v>
+      </c>
+      <c r="AB12" s="74"/>
+      <c r="AC12" s="74"/>
+      <c r="AD12" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="Z11" s="41">
-        <v>0</v>
-      </c>
-      <c r="AA11" s="39" t="s">
-        <v>34</v>
-      </c>
-      <c r="AB11" s="41">
-        <v>0</v>
-      </c>
-      <c r="AC11" s="39" t="s">
-        <v>35</v>
-      </c>
-      <c r="AD11" s="41">
-        <v>0</v>
-      </c>
-      <c r="AE11" s="42" t="s">
-        <v>36</v>
-      </c>
-      <c r="AF11" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="12" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A12" s="52"/>
-      <c r="B12" s="24" t="s">
-        <v>30</v>
-      </c>
-      <c r="C12" s="55">
-        <v>0</v>
-      </c>
-      <c r="D12" s="56"/>
-      <c r="E12" s="40" t="s">
-        <v>44</v>
-      </c>
-      <c r="F12" s="29"/>
-      <c r="G12" s="56">
-        <v>0</v>
-      </c>
-      <c r="H12" s="56"/>
-      <c r="I12" s="56"/>
-      <c r="J12" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="K12" s="30"/>
-      <c r="L12" s="55">
-        <v>0</v>
-      </c>
-      <c r="M12" s="56"/>
-      <c r="N12" s="40" t="s">
-        <v>44</v>
-      </c>
-      <c r="O12" s="29"/>
-      <c r="P12" s="56">
-        <v>0</v>
-      </c>
-      <c r="Q12" s="56"/>
-      <c r="R12" s="56"/>
-      <c r="S12" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="T12" s="30"/>
-      <c r="U12" s="52"/>
-      <c r="V12" s="24" t="s">
-        <v>30</v>
-      </c>
-      <c r="W12" s="55">
-        <v>0</v>
-      </c>
-      <c r="X12" s="56"/>
-      <c r="Y12" s="40" t="s">
-        <v>44</v>
-      </c>
-      <c r="Z12" s="29"/>
-      <c r="AA12" s="56">
-        <v>0</v>
-      </c>
-      <c r="AB12" s="56"/>
-      <c r="AC12" s="56"/>
-      <c r="AD12" s="5" t="s">
-        <v>38</v>
-      </c>
       <c r="AE12" s="30"/>
     </row>
     <row r="13" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A13" s="52"/>
+      <c r="A13" s="77"/>
       <c r="B13" s="23" t="s">
         <v>10</v>
       </c>
@@ -3801,19 +3801,19 @@
         <v>73.2</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E13" s="3">
         <v>145.5</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G13" s="1">
         <v>6.61</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I13" s="2" t="s">
         <v>11</v>
@@ -3828,19 +3828,19 @@
         <v>70</v>
       </c>
       <c r="M13" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="N13" s="3">
         <v>138.5</v>
       </c>
       <c r="O13" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="P13" s="1">
         <v>6.18</v>
       </c>
       <c r="Q13" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="R13" s="2" t="s">
         <v>11</v>
@@ -3851,7 +3851,7 @@
       <c r="T13" s="21" t="s">
         <v>5</v>
       </c>
-      <c r="U13" s="52"/>
+      <c r="U13" s="77"/>
       <c r="V13" s="23" t="s">
         <v>10</v>
       </c>
@@ -3859,19 +3859,19 @@
         <v>56.4</v>
       </c>
       <c r="X13" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="Y13" s="3">
         <v>111.5</v>
       </c>
       <c r="Z13" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AA13" s="1">
         <v>4.7300000000000004</v>
       </c>
       <c r="AB13" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AC13" s="2" t="s">
         <v>11</v>
@@ -3884,7 +3884,7 @@
       </c>
     </row>
     <row r="14" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A14" s="52"/>
+      <c r="A14" s="77"/>
       <c r="B14" s="23" t="s">
         <v>8</v>
       </c>
@@ -3892,7 +3892,7 @@
         <v>29.5</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I14" s="2" t="s">
         <v>11</v>
@@ -3907,7 +3907,7 @@
         <v>38.200000000000003</v>
       </c>
       <c r="M14" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="R14" s="2" t="s">
         <v>11</v>
@@ -3918,7 +3918,7 @@
       <c r="T14" s="21" t="s">
         <v>5</v>
       </c>
-      <c r="U14" s="52"/>
+      <c r="U14" s="77"/>
       <c r="V14" s="23" t="s">
         <v>8</v>
       </c>
@@ -3926,7 +3926,7 @@
         <v>45.8</v>
       </c>
       <c r="X14" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AC14" s="2" t="s">
         <v>11</v>
@@ -3939,24 +3939,24 @@
       </c>
     </row>
     <row r="15" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A15" s="52"/>
+      <c r="A15" s="77"/>
       <c r="B15" s="23" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C15" s="36">
         <v>33.9</v>
       </c>
       <c r="D15" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E15" s="28" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G15" s="1">
         <v>29</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I15" s="2" t="s">
         <v>11</v>
@@ -3971,16 +3971,16 @@
         <v>26.4</v>
       </c>
       <c r="M15" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="N15" s="28" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="P15" s="1">
         <v>38</v>
       </c>
       <c r="Q15" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="R15" s="2" t="s">
         <v>11</v>
@@ -3991,24 +3991,24 @@
       <c r="T15" s="21" t="s">
         <v>5</v>
       </c>
-      <c r="U15" s="52"/>
+      <c r="U15" s="77"/>
       <c r="V15" s="23" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="W15" s="36">
         <v>22.5</v>
       </c>
       <c r="X15" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y15" s="28" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AA15" s="1">
         <v>45</v>
       </c>
       <c r="AB15" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AC15" s="2" t="s">
         <v>11</v>
@@ -4021,7 +4021,7 @@
       </c>
     </row>
     <row r="16" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A16" s="52"/>
+      <c r="A16" s="77"/>
       <c r="B16" s="23" t="s">
         <v>9</v>
       </c>
@@ -4049,7 +4049,7 @@
       <c r="T16" s="21" t="s">
         <v>5</v>
       </c>
-      <c r="U16" s="52"/>
+      <c r="U16" s="77"/>
       <c r="V16" s="23" t="s">
         <v>9</v>
       </c>
@@ -4067,15 +4067,15 @@
       </c>
     </row>
     <row r="17" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A17" s="52"/>
+      <c r="A17" s="77"/>
       <c r="B17" s="24" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C17" s="37">
         <v>315.8</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E17" s="6"/>
       <c r="F17" s="5"/>
@@ -4094,7 +4094,7 @@
         <v>334.2</v>
       </c>
       <c r="M17" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="N17" s="6"/>
       <c r="O17" s="5"/>
@@ -4109,15 +4109,15 @@
       <c r="T17" s="22" t="s">
         <v>5</v>
       </c>
-      <c r="U17" s="52"/>
+      <c r="U17" s="77"/>
       <c r="V17" s="24" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="W17" s="37">
         <v>354.5</v>
       </c>
       <c r="X17" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Y17" s="6"/>
       <c r="Z17" s="5"/>
@@ -4134,157 +4134,157 @@
       </c>
     </row>
     <row r="18" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="52" t="s">
-        <v>56</v>
+      <c r="A18" s="77" t="s">
+        <v>55</v>
       </c>
       <c r="B18" s="27" t="s">
-        <v>31</v>
-      </c>
-      <c r="C18" s="53" t="s">
-        <v>40</v>
-      </c>
-      <c r="D18" s="54"/>
+        <v>30</v>
+      </c>
+      <c r="C18" s="75" t="s">
+        <v>39</v>
+      </c>
+      <c r="D18" s="76"/>
       <c r="E18" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="F18" s="41">
+        <v>0</v>
+      </c>
+      <c r="G18" s="39" t="s">
+        <v>33</v>
+      </c>
+      <c r="H18" s="41">
+        <v>0</v>
+      </c>
+      <c r="I18" s="39" t="s">
+        <v>34</v>
+      </c>
+      <c r="J18" s="41">
+        <v>0</v>
+      </c>
+      <c r="K18" s="39" t="s">
+        <v>35</v>
+      </c>
+      <c r="L18" s="75" t="s">
+        <v>39</v>
+      </c>
+      <c r="M18" s="76"/>
+      <c r="N18" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="O18" s="41">
+        <v>0</v>
+      </c>
+      <c r="P18" s="39" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q18" s="41">
+        <v>0</v>
+      </c>
+      <c r="R18" s="39" t="s">
+        <v>34</v>
+      </c>
+      <c r="S18" s="41">
+        <v>0</v>
+      </c>
+      <c r="T18" s="39" t="s">
+        <v>35</v>
+      </c>
+      <c r="U18" s="77" t="s">
+        <v>55</v>
+      </c>
+      <c r="V18" s="27" t="s">
+        <v>30</v>
+      </c>
+      <c r="W18" s="75" t="s">
+        <v>39</v>
+      </c>
+      <c r="X18" s="76"/>
+      <c r="Y18" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="Z18" s="41">
+        <v>0</v>
+      </c>
+      <c r="AA18" s="39" t="s">
+        <v>33</v>
+      </c>
+      <c r="AB18" s="41">
+        <v>0</v>
+      </c>
+      <c r="AC18" s="39" t="s">
+        <v>34</v>
+      </c>
+      <c r="AD18" s="41">
+        <v>0</v>
+      </c>
+      <c r="AE18" s="42" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="19" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A19" s="77"/>
+      <c r="B19" s="24" t="s">
+        <v>29</v>
+      </c>
+      <c r="C19" s="78">
+        <v>0</v>
+      </c>
+      <c r="D19" s="74"/>
+      <c r="E19" s="40" t="s">
+        <v>43</v>
+      </c>
+      <c r="F19" s="29"/>
+      <c r="G19" s="74">
+        <v>0</v>
+      </c>
+      <c r="H19" s="74"/>
+      <c r="I19" s="74"/>
+      <c r="J19" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="F18" s="41">
-        <v>0</v>
-      </c>
-      <c r="G18" s="39" t="s">
-        <v>34</v>
-      </c>
-      <c r="H18" s="41">
-        <v>0</v>
-      </c>
-      <c r="I18" s="39" t="s">
-        <v>35</v>
-      </c>
-      <c r="J18" s="41">
-        <v>0</v>
-      </c>
-      <c r="K18" s="39" t="s">
-        <v>36</v>
-      </c>
-      <c r="L18" s="53" t="s">
-        <v>40</v>
-      </c>
-      <c r="M18" s="54"/>
-      <c r="N18" s="7" t="s">
+      <c r="K19" s="30"/>
+      <c r="L19" s="78">
+        <v>0</v>
+      </c>
+      <c r="M19" s="74"/>
+      <c r="N19" s="40" t="s">
+        <v>43</v>
+      </c>
+      <c r="O19" s="29"/>
+      <c r="P19" s="74">
+        <v>0</v>
+      </c>
+      <c r="Q19" s="74"/>
+      <c r="R19" s="74"/>
+      <c r="S19" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="O18" s="41">
-        <v>0</v>
-      </c>
-      <c r="P18" s="39" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q18" s="41">
-        <v>0</v>
-      </c>
-      <c r="R18" s="39" t="s">
-        <v>35</v>
-      </c>
-      <c r="S18" s="41">
-        <v>0</v>
-      </c>
-      <c r="T18" s="39" t="s">
-        <v>36</v>
-      </c>
-      <c r="U18" s="52" t="s">
-        <v>56</v>
-      </c>
-      <c r="V18" s="27" t="s">
-        <v>31</v>
-      </c>
-      <c r="W18" s="53" t="s">
-        <v>40</v>
-      </c>
-      <c r="X18" s="54"/>
-      <c r="Y18" s="7" t="s">
+      <c r="T19" s="30"/>
+      <c r="U19" s="77"/>
+      <c r="V19" s="24" t="s">
+        <v>29</v>
+      </c>
+      <c r="W19" s="78">
+        <v>0</v>
+      </c>
+      <c r="X19" s="74"/>
+      <c r="Y19" s="40" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z19" s="29"/>
+      <c r="AA19" s="74">
+        <v>0</v>
+      </c>
+      <c r="AB19" s="74"/>
+      <c r="AC19" s="74"/>
+      <c r="AD19" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="Z18" s="41">
-        <v>0</v>
-      </c>
-      <c r="AA18" s="39" t="s">
-        <v>34</v>
-      </c>
-      <c r="AB18" s="41">
-        <v>0</v>
-      </c>
-      <c r="AC18" s="39" t="s">
-        <v>35</v>
-      </c>
-      <c r="AD18" s="41">
-        <v>0</v>
-      </c>
-      <c r="AE18" s="42" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="19" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A19" s="52"/>
-      <c r="B19" s="24" t="s">
-        <v>30</v>
-      </c>
-      <c r="C19" s="55">
-        <v>0</v>
-      </c>
-      <c r="D19" s="56"/>
-      <c r="E19" s="40" t="s">
-        <v>44</v>
-      </c>
-      <c r="F19" s="29"/>
-      <c r="G19" s="56">
-        <v>0</v>
-      </c>
-      <c r="H19" s="56"/>
-      <c r="I19" s="56"/>
-      <c r="J19" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="K19" s="30"/>
-      <c r="L19" s="55">
-        <v>0</v>
-      </c>
-      <c r="M19" s="56"/>
-      <c r="N19" s="40" t="s">
-        <v>44</v>
-      </c>
-      <c r="O19" s="29"/>
-      <c r="P19" s="56">
-        <v>0</v>
-      </c>
-      <c r="Q19" s="56"/>
-      <c r="R19" s="56"/>
-      <c r="S19" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="T19" s="30"/>
-      <c r="U19" s="52"/>
-      <c r="V19" s="24" t="s">
-        <v>30</v>
-      </c>
-      <c r="W19" s="55">
-        <v>0</v>
-      </c>
-      <c r="X19" s="56"/>
-      <c r="Y19" s="40" t="s">
-        <v>44</v>
-      </c>
-      <c r="Z19" s="29"/>
-      <c r="AA19" s="56">
-        <v>0</v>
-      </c>
-      <c r="AB19" s="56"/>
-      <c r="AC19" s="56"/>
-      <c r="AD19" s="5" t="s">
-        <v>38</v>
-      </c>
       <c r="AE19" s="30"/>
     </row>
     <row r="20" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A20" s="52"/>
+      <c r="A20" s="77"/>
       <c r="B20" s="23" t="s">
         <v>10</v>
       </c>
@@ -4292,19 +4292,19 @@
         <v>70.599999999999994</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E20" s="3">
         <v>140.5</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G20" s="1">
         <v>4.49</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I20" s="2" t="s">
         <v>11</v>
@@ -4319,19 +4319,19 @@
         <v>21.2</v>
       </c>
       <c r="M20" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="N20" s="3">
         <v>41.8</v>
       </c>
       <c r="O20" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="P20" s="1">
         <v>1.28</v>
       </c>
       <c r="Q20" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="R20" s="2" t="s">
         <v>11</v>
@@ -4342,7 +4342,7 @@
       <c r="T20" s="21" t="s">
         <v>5</v>
       </c>
-      <c r="U20" s="52"/>
+      <c r="U20" s="77"/>
       <c r="V20" s="23" t="s">
         <v>10</v>
       </c>
@@ -4350,19 +4350,19 @@
         <v>18.8</v>
       </c>
       <c r="X20" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="Y20" s="3">
         <v>37.4</v>
       </c>
       <c r="Z20" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AA20" s="1">
         <v>1.17</v>
       </c>
       <c r="AB20" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AC20" s="2" t="s">
         <v>11</v>
@@ -4375,7 +4375,7 @@
       </c>
     </row>
     <row r="21" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A21" s="52"/>
+      <c r="A21" s="77"/>
       <c r="B21" s="23" t="s">
         <v>8</v>
       </c>
@@ -4383,7 +4383,7 @@
         <v>34.799999999999997</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I21" s="2" t="s">
         <v>11</v>
@@ -4398,7 +4398,7 @@
         <v>46.1</v>
       </c>
       <c r="M21" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="R21" s="2" t="s">
         <v>11</v>
@@ -4409,7 +4409,7 @@
       <c r="T21" s="21" t="s">
         <v>5</v>
       </c>
-      <c r="U21" s="52"/>
+      <c r="U21" s="77"/>
       <c r="V21" s="23" t="s">
         <v>8</v>
       </c>
@@ -4417,7 +4417,7 @@
         <v>43.1</v>
       </c>
       <c r="X21" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AC21" s="2" t="s">
         <v>11</v>
@@ -4430,24 +4430,24 @@
       </c>
     </row>
     <row r="22" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A22" s="52"/>
+      <c r="A22" s="77"/>
       <c r="B22" s="23" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C22" s="36">
         <v>28.7</v>
       </c>
       <c r="D22" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E22" s="28" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G22" s="1">
         <v>35</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I22" s="2" t="s">
         <v>11</v>
@@ -4462,16 +4462,16 @@
         <v>21.7</v>
       </c>
       <c r="M22" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="N22" s="28" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="P22" s="1">
         <v>46</v>
       </c>
       <c r="Q22" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="R22" s="2" t="s">
         <v>11</v>
@@ -4482,24 +4482,24 @@
       <c r="T22" s="21" t="s">
         <v>5</v>
       </c>
-      <c r="U22" s="52"/>
+      <c r="U22" s="77"/>
       <c r="V22" s="23" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="W22" s="36">
         <v>23.2</v>
       </c>
       <c r="X22" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y22" s="28" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AA22" s="1">
         <v>43</v>
       </c>
       <c r="AB22" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AC22" s="2" t="s">
         <v>11</v>
@@ -4512,7 +4512,7 @@
       </c>
     </row>
     <row r="23" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A23" s="52"/>
+      <c r="A23" s="77"/>
       <c r="B23" s="23" t="s">
         <v>9</v>
       </c>
@@ -4540,7 +4540,7 @@
       <c r="T23" s="21" t="s">
         <v>5</v>
       </c>
-      <c r="U23" s="52"/>
+      <c r="U23" s="77"/>
       <c r="V23" s="23" t="s">
         <v>9</v>
       </c>
@@ -4558,15 +4558,15 @@
       </c>
     </row>
     <row r="24" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A24" s="52"/>
+      <c r="A24" s="77"/>
       <c r="B24" s="24" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C24" s="37">
         <v>359.4</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E24" s="6"/>
       <c r="F24" s="5"/>
@@ -4585,7 +4585,7 @@
         <v>239.8</v>
       </c>
       <c r="M24" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="N24" s="6"/>
       <c r="O24" s="5"/>
@@ -4600,15 +4600,15 @@
       <c r="T24" s="22" t="s">
         <v>5</v>
       </c>
-      <c r="U24" s="52"/>
+      <c r="U24" s="77"/>
       <c r="V24" s="24" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="W24" s="37">
         <v>191.8</v>
       </c>
       <c r="X24" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Y24" s="6"/>
       <c r="Z24" s="5"/>
@@ -4625,157 +4625,157 @@
       </c>
     </row>
     <row r="25" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="57" t="s">
-        <v>62</v>
+      <c r="A25" s="82" t="s">
+        <v>61</v>
       </c>
       <c r="B25" s="27" t="s">
-        <v>31</v>
-      </c>
-      <c r="C25" s="53" t="s">
-        <v>40</v>
-      </c>
-      <c r="D25" s="54"/>
+        <v>30</v>
+      </c>
+      <c r="C25" s="75" t="s">
+        <v>39</v>
+      </c>
+      <c r="D25" s="76"/>
       <c r="E25" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="F25" s="41">
+        <v>0</v>
+      </c>
+      <c r="G25" s="39" t="s">
+        <v>33</v>
+      </c>
+      <c r="H25" s="41">
+        <v>0</v>
+      </c>
+      <c r="I25" s="39" t="s">
+        <v>34</v>
+      </c>
+      <c r="J25" s="41">
+        <v>0</v>
+      </c>
+      <c r="K25" s="39" t="s">
+        <v>35</v>
+      </c>
+      <c r="L25" s="75" t="s">
+        <v>39</v>
+      </c>
+      <c r="M25" s="76"/>
+      <c r="N25" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="O25" s="41">
+        <v>0</v>
+      </c>
+      <c r="P25" s="39" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q25" s="41">
+        <v>0</v>
+      </c>
+      <c r="R25" s="39" t="s">
+        <v>34</v>
+      </c>
+      <c r="S25" s="41">
+        <v>0</v>
+      </c>
+      <c r="T25" s="39" t="s">
+        <v>35</v>
+      </c>
+      <c r="U25" s="77" t="s">
+        <v>61</v>
+      </c>
+      <c r="V25" s="27" t="s">
+        <v>30</v>
+      </c>
+      <c r="W25" s="75" t="s">
+        <v>39</v>
+      </c>
+      <c r="X25" s="76"/>
+      <c r="Y25" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="Z25" s="41">
+        <v>0</v>
+      </c>
+      <c r="AA25" s="39" t="s">
+        <v>33</v>
+      </c>
+      <c r="AB25" s="41">
+        <v>0</v>
+      </c>
+      <c r="AC25" s="39" t="s">
+        <v>34</v>
+      </c>
+      <c r="AD25" s="41">
+        <v>0</v>
+      </c>
+      <c r="AE25" s="42" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="26" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A26" s="83"/>
+      <c r="B26" s="24" t="s">
+        <v>29</v>
+      </c>
+      <c r="C26" s="78">
+        <v>0</v>
+      </c>
+      <c r="D26" s="74"/>
+      <c r="E26" s="40" t="s">
+        <v>43</v>
+      </c>
+      <c r="F26" s="29"/>
+      <c r="G26" s="74">
+        <v>0</v>
+      </c>
+      <c r="H26" s="74"/>
+      <c r="I26" s="74"/>
+      <c r="J26" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="F25" s="41">
-        <v>0</v>
-      </c>
-      <c r="G25" s="39" t="s">
-        <v>34</v>
-      </c>
-      <c r="H25" s="41">
-        <v>0</v>
-      </c>
-      <c r="I25" s="39" t="s">
-        <v>35</v>
-      </c>
-      <c r="J25" s="41">
-        <v>0</v>
-      </c>
-      <c r="K25" s="39" t="s">
-        <v>36</v>
-      </c>
-      <c r="L25" s="53" t="s">
-        <v>40</v>
-      </c>
-      <c r="M25" s="54"/>
-      <c r="N25" s="7" t="s">
+      <c r="K26" s="30"/>
+      <c r="L26" s="78">
+        <v>0</v>
+      </c>
+      <c r="M26" s="74"/>
+      <c r="N26" s="40" t="s">
+        <v>43</v>
+      </c>
+      <c r="O26" s="29"/>
+      <c r="P26" s="74">
+        <v>0</v>
+      </c>
+      <c r="Q26" s="74"/>
+      <c r="R26" s="74"/>
+      <c r="S26" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="O25" s="41">
-        <v>0</v>
-      </c>
-      <c r="P25" s="39" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q25" s="41">
-        <v>0</v>
-      </c>
-      <c r="R25" s="39" t="s">
-        <v>35</v>
-      </c>
-      <c r="S25" s="41">
-        <v>0</v>
-      </c>
-      <c r="T25" s="39" t="s">
-        <v>36</v>
-      </c>
-      <c r="U25" s="52" t="s">
-        <v>62</v>
-      </c>
-      <c r="V25" s="27" t="s">
-        <v>31</v>
-      </c>
-      <c r="W25" s="53" t="s">
-        <v>40</v>
-      </c>
-      <c r="X25" s="54"/>
-      <c r="Y25" s="7" t="s">
+      <c r="T26" s="30"/>
+      <c r="U26" s="77"/>
+      <c r="V26" s="24" t="s">
+        <v>29</v>
+      </c>
+      <c r="W26" s="78">
+        <v>0</v>
+      </c>
+      <c r="X26" s="74"/>
+      <c r="Y26" s="40" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z26" s="29"/>
+      <c r="AA26" s="74">
+        <v>0</v>
+      </c>
+      <c r="AB26" s="74"/>
+      <c r="AC26" s="74"/>
+      <c r="AD26" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="Z25" s="41">
-        <v>0</v>
-      </c>
-      <c r="AA25" s="39" t="s">
-        <v>34</v>
-      </c>
-      <c r="AB25" s="41">
-        <v>0</v>
-      </c>
-      <c r="AC25" s="39" t="s">
-        <v>35</v>
-      </c>
-      <c r="AD25" s="41">
-        <v>0</v>
-      </c>
-      <c r="AE25" s="42" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="26" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A26" s="58"/>
-      <c r="B26" s="24" t="s">
-        <v>30</v>
-      </c>
-      <c r="C26" s="55">
-        <v>0</v>
-      </c>
-      <c r="D26" s="56"/>
-      <c r="E26" s="40" t="s">
-        <v>44</v>
-      </c>
-      <c r="F26" s="29"/>
-      <c r="G26" s="56">
-        <v>0</v>
-      </c>
-      <c r="H26" s="56"/>
-      <c r="I26" s="56"/>
-      <c r="J26" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="K26" s="30"/>
-      <c r="L26" s="55">
-        <v>0</v>
-      </c>
-      <c r="M26" s="56"/>
-      <c r="N26" s="40" t="s">
-        <v>44</v>
-      </c>
-      <c r="O26" s="29"/>
-      <c r="P26" s="56">
-        <v>0</v>
-      </c>
-      <c r="Q26" s="56"/>
-      <c r="R26" s="56"/>
-      <c r="S26" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="T26" s="30"/>
-      <c r="U26" s="52"/>
-      <c r="V26" s="24" t="s">
-        <v>30</v>
-      </c>
-      <c r="W26" s="55">
-        <v>0</v>
-      </c>
-      <c r="X26" s="56"/>
-      <c r="Y26" s="40" t="s">
-        <v>44</v>
-      </c>
-      <c r="Z26" s="29"/>
-      <c r="AA26" s="56">
-        <v>0</v>
-      </c>
-      <c r="AB26" s="56"/>
-      <c r="AC26" s="56"/>
-      <c r="AD26" s="5" t="s">
-        <v>38</v>
-      </c>
       <c r="AE26" s="30"/>
     </row>
     <row r="27" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A27" s="58"/>
+      <c r="A27" s="83"/>
       <c r="B27" s="23" t="s">
         <v>10</v>
       </c>
@@ -4783,19 +4783,19 @@
         <v>64.7</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E27" s="3">
         <v>130.9</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G27" s="1">
         <v>4.6900000000000004</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I27" s="2" t="s">
         <v>11</v>
@@ -4810,19 +4810,19 @@
         <v>87.9</v>
       </c>
       <c r="M27" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="N27" s="3">
         <v>178.3</v>
       </c>
       <c r="O27" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="P27" s="1">
         <v>6.22</v>
       </c>
       <c r="Q27" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="R27" s="2" t="s">
         <v>11</v>
@@ -4833,7 +4833,7 @@
       <c r="T27" s="21" t="s">
         <v>5</v>
       </c>
-      <c r="U27" s="52"/>
+      <c r="U27" s="77"/>
       <c r="V27" s="23" t="s">
         <v>10</v>
       </c>
@@ -4841,19 +4841,19 @@
         <v>78.400000000000006</v>
       </c>
       <c r="X27" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="Y27" s="3">
         <v>158.19999999999999</v>
       </c>
       <c r="Z27" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AA27" s="1">
         <v>5.54</v>
       </c>
       <c r="AB27" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AC27" s="2" t="s">
         <v>11</v>
@@ -4866,7 +4866,7 @@
       </c>
     </row>
     <row r="28" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A28" s="58"/>
+      <c r="A28" s="83"/>
       <c r="B28" s="23" t="s">
         <v>8</v>
       </c>
@@ -4874,7 +4874,7 @@
         <v>30</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I28" s="2" t="s">
         <v>11</v>
@@ -4889,7 +4889,7 @@
         <v>32.200000000000003</v>
       </c>
       <c r="M28" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="R28" s="2" t="s">
         <v>11</v>
@@ -4900,7 +4900,7 @@
       <c r="T28" s="21" t="s">
         <v>5</v>
       </c>
-      <c r="U28" s="52"/>
+      <c r="U28" s="77"/>
       <c r="V28" s="23" t="s">
         <v>8</v>
       </c>
@@ -4908,7 +4908,7 @@
         <v>35.299999999999997</v>
       </c>
       <c r="X28" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AC28" s="2" t="s">
         <v>11</v>
@@ -4921,24 +4921,24 @@
       </c>
     </row>
     <row r="29" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A29" s="58"/>
+      <c r="A29" s="83"/>
       <c r="B29" s="23" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C29" s="36">
         <v>33.799999999999997</v>
       </c>
       <c r="D29" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E29" s="28" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G29" s="1">
         <v>30</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I29" s="2" t="s">
         <v>11</v>
@@ -4953,16 +4953,16 @@
         <v>31.1</v>
       </c>
       <c r="M29" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="N29" s="28" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="P29" s="1">
         <v>32</v>
       </c>
       <c r="Q29" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="R29" s="2" t="s">
         <v>11</v>
@@ -4973,24 +4973,24 @@
       <c r="T29" s="21" t="s">
         <v>5</v>
       </c>
-      <c r="U29" s="52"/>
+      <c r="U29" s="77"/>
       <c r="V29" s="23" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="W29" s="36">
         <v>28</v>
       </c>
       <c r="X29" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y29" s="28" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AA29" s="1">
         <v>36</v>
       </c>
       <c r="AB29" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AC29" s="2" t="s">
         <v>11</v>
@@ -5003,7 +5003,7 @@
       </c>
     </row>
     <row r="30" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A30" s="58"/>
+      <c r="A30" s="83"/>
       <c r="B30" s="23" t="s">
         <v>9</v>
       </c>
@@ -5031,7 +5031,7 @@
       <c r="T30" s="21" t="s">
         <v>5</v>
       </c>
-      <c r="U30" s="52"/>
+      <c r="U30" s="77"/>
       <c r="V30" s="23" t="s">
         <v>9</v>
       </c>
@@ -5049,15 +5049,15 @@
       </c>
     </row>
     <row r="31" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A31" s="59"/>
+      <c r="A31" s="84"/>
       <c r="B31" s="24" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C31" s="37">
         <v>288.2</v>
       </c>
       <c r="D31" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E31" s="6"/>
       <c r="F31" s="5"/>
@@ -5076,7 +5076,7 @@
         <v>281.7</v>
       </c>
       <c r="M31" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="N31" s="6"/>
       <c r="O31" s="5"/>
@@ -5091,15 +5091,15 @@
       <c r="T31" s="22" t="s">
         <v>5</v>
       </c>
-      <c r="U31" s="52"/>
+      <c r="U31" s="77"/>
       <c r="V31" s="24" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="W31" s="37">
         <v>297.39999999999998</v>
       </c>
       <c r="X31" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Y31" s="6"/>
       <c r="Z31" s="5"/>
@@ -5117,20 +5117,33 @@
     </row>
     <row r="33" spans="12:12" x14ac:dyDescent="0.25">
       <c r="L33" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="47">
-    <mergeCell ref="W25:X25"/>
-    <mergeCell ref="W26:X26"/>
-    <mergeCell ref="AA26:AC26"/>
-    <mergeCell ref="W11:X11"/>
-    <mergeCell ref="W12:X12"/>
-    <mergeCell ref="AA12:AC12"/>
-    <mergeCell ref="W18:X18"/>
-    <mergeCell ref="W19:X19"/>
-    <mergeCell ref="AA19:AC19"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="G26:I26"/>
+    <mergeCell ref="C3:K3"/>
+    <mergeCell ref="L3:T3"/>
+    <mergeCell ref="L25:M25"/>
+    <mergeCell ref="L26:M26"/>
+    <mergeCell ref="P26:R26"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="G12:I12"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="L19:M19"/>
+    <mergeCell ref="P19:R19"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="G19:I19"/>
+    <mergeCell ref="W3:AE3"/>
+    <mergeCell ref="A4:A10"/>
+    <mergeCell ref="U4:U10"/>
+    <mergeCell ref="W4:X4"/>
+    <mergeCell ref="W5:X5"/>
+    <mergeCell ref="AA5:AC5"/>
     <mergeCell ref="A18:A24"/>
     <mergeCell ref="U18:U24"/>
     <mergeCell ref="A25:A31"/>
@@ -5147,28 +5160,15 @@
     <mergeCell ref="L12:M12"/>
     <mergeCell ref="P12:R12"/>
     <mergeCell ref="L18:M18"/>
-    <mergeCell ref="W3:AE3"/>
-    <mergeCell ref="A4:A10"/>
-    <mergeCell ref="U4:U10"/>
-    <mergeCell ref="W4:X4"/>
-    <mergeCell ref="W5:X5"/>
-    <mergeCell ref="AA5:AC5"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="C26:D26"/>
-    <mergeCell ref="G26:I26"/>
-    <mergeCell ref="C3:K3"/>
-    <mergeCell ref="L3:T3"/>
-    <mergeCell ref="L25:M25"/>
-    <mergeCell ref="L26:M26"/>
-    <mergeCell ref="P26:R26"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="G12:I12"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="L19:M19"/>
-    <mergeCell ref="P19:R19"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="G19:I19"/>
+    <mergeCell ref="W25:X25"/>
+    <mergeCell ref="W26:X26"/>
+    <mergeCell ref="AA26:AC26"/>
+    <mergeCell ref="W11:X11"/>
+    <mergeCell ref="W12:X12"/>
+    <mergeCell ref="AA12:AC12"/>
+    <mergeCell ref="W18:X18"/>
+    <mergeCell ref="W19:X19"/>
+    <mergeCell ref="AA19:AC19"/>
   </mergeCells>
   <pageMargins left="0.19685039370078741" right="0.11811023622047245" top="0.78740157480314965" bottom="0.78740157480314965" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>
@@ -5247,231 +5247,231 @@
         <v>0</v>
       </c>
       <c r="B3" s="32" t="s">
+        <v>31</v>
+      </c>
+      <c r="C3" s="79" t="s">
+        <v>4</v>
+      </c>
+      <c r="D3" s="80"/>
+      <c r="E3" s="80"/>
+      <c r="F3" s="80"/>
+      <c r="G3" s="80"/>
+      <c r="H3" s="80"/>
+      <c r="I3" s="80"/>
+      <c r="J3" s="80"/>
+      <c r="K3" s="81"/>
+      <c r="L3" s="79" t="s">
+        <v>6</v>
+      </c>
+      <c r="M3" s="80"/>
+      <c r="N3" s="80"/>
+      <c r="O3" s="80"/>
+      <c r="P3" s="80"/>
+      <c r="Q3" s="80"/>
+      <c r="R3" s="80"/>
+      <c r="S3" s="80"/>
+      <c r="T3" s="81"/>
+      <c r="U3" s="31" t="s">
+        <v>0</v>
+      </c>
+      <c r="V3" s="32" t="s">
+        <v>31</v>
+      </c>
+      <c r="W3" s="79" t="s">
+        <v>7</v>
+      </c>
+      <c r="X3" s="80"/>
+      <c r="Y3" s="80"/>
+      <c r="Z3" s="80"/>
+      <c r="AA3" s="80"/>
+      <c r="AB3" s="80"/>
+      <c r="AC3" s="80"/>
+      <c r="AD3" s="80"/>
+      <c r="AE3" s="81"/>
+      <c r="AF3" s="79" t="s">
         <v>32</v>
       </c>
-      <c r="C3" s="49" t="s">
-        <v>4</v>
-      </c>
-      <c r="D3" s="50"/>
-      <c r="E3" s="50"/>
-      <c r="F3" s="50"/>
-      <c r="G3" s="50"/>
-      <c r="H3" s="50"/>
-      <c r="I3" s="50"/>
-      <c r="J3" s="50"/>
-      <c r="K3" s="51"/>
-      <c r="L3" s="49" t="s">
-        <v>6</v>
-      </c>
-      <c r="M3" s="50"/>
-      <c r="N3" s="50"/>
-      <c r="O3" s="50"/>
-      <c r="P3" s="50"/>
-      <c r="Q3" s="50"/>
-      <c r="R3" s="50"/>
-      <c r="S3" s="50"/>
-      <c r="T3" s="51"/>
-      <c r="U3" s="31" t="s">
-        <v>0</v>
-      </c>
-      <c r="V3" s="32" t="s">
-        <v>32</v>
-      </c>
-      <c r="W3" s="49" t="s">
-        <v>7</v>
-      </c>
-      <c r="X3" s="50"/>
-      <c r="Y3" s="50"/>
-      <c r="Z3" s="50"/>
-      <c r="AA3" s="50"/>
-      <c r="AB3" s="50"/>
-      <c r="AC3" s="50"/>
-      <c r="AD3" s="50"/>
-      <c r="AE3" s="51"/>
-      <c r="AF3" s="49" t="s">
+      <c r="AG3" s="80"/>
+      <c r="AH3" s="80"/>
+      <c r="AI3" s="80"/>
+      <c r="AJ3" s="80"/>
+      <c r="AK3" s="80"/>
+      <c r="AL3" s="80"/>
+      <c r="AM3" s="80"/>
+      <c r="AN3" s="81"/>
+    </row>
+    <row r="4" spans="1:40" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="77" t="s">
+        <v>41</v>
+      </c>
+      <c r="B4" s="27" t="s">
+        <v>30</v>
+      </c>
+      <c r="C4" s="75" t="s">
+        <v>39</v>
+      </c>
+      <c r="D4" s="76"/>
+      <c r="E4" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="F4">
+        <v>0</v>
+      </c>
+      <c r="G4" s="39" t="s">
         <v>33</v>
       </c>
-      <c r="AG3" s="50"/>
-      <c r="AH3" s="50"/>
-      <c r="AI3" s="50"/>
-      <c r="AJ3" s="50"/>
-      <c r="AK3" s="50"/>
-      <c r="AL3" s="50"/>
-      <c r="AM3" s="50"/>
-      <c r="AN3" s="51"/>
-    </row>
-    <row r="4" spans="1:40" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="52" t="s">
-        <v>42</v>
-      </c>
-      <c r="B4" s="27" t="s">
-        <v>31</v>
-      </c>
-      <c r="C4" s="53" t="s">
-        <v>40</v>
-      </c>
-      <c r="D4" s="54"/>
-      <c r="E4" s="2" t="s">
+      <c r="H4" s="41">
+        <v>0</v>
+      </c>
+      <c r="I4" s="39" t="s">
+        <v>34</v>
+      </c>
+      <c r="J4" s="41">
+        <v>0</v>
+      </c>
+      <c r="K4" s="39" t="s">
+        <v>35</v>
+      </c>
+      <c r="L4" s="75" t="s">
+        <v>39</v>
+      </c>
+      <c r="M4" s="76"/>
+      <c r="N4" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="O4" s="41">
+        <v>0</v>
+      </c>
+      <c r="P4" s="39" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q4" s="41">
+        <v>0</v>
+      </c>
+      <c r="R4" s="39" t="s">
+        <v>34</v>
+      </c>
+      <c r="S4" s="41">
+        <v>0</v>
+      </c>
+      <c r="T4" s="42" t="s">
+        <v>35</v>
+      </c>
+      <c r="U4" s="77" t="s">
+        <v>41</v>
+      </c>
+      <c r="V4" s="27" t="s">
+        <v>30</v>
+      </c>
+      <c r="W4" s="75" t="s">
+        <v>39</v>
+      </c>
+      <c r="X4" s="76"/>
+      <c r="Y4" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="Z4">
+        <v>0</v>
+      </c>
+      <c r="AA4" s="39" t="s">
+        <v>33</v>
+      </c>
+      <c r="AB4" s="41">
+        <v>0</v>
+      </c>
+      <c r="AC4" s="39" t="s">
+        <v>34</v>
+      </c>
+      <c r="AD4" s="41">
+        <v>0</v>
+      </c>
+      <c r="AE4" s="39" t="s">
+        <v>35</v>
+      </c>
+      <c r="AF4" s="85" t="s">
+        <v>38</v>
+      </c>
+      <c r="AG4" s="86"/>
+      <c r="AH4" s="86"/>
+      <c r="AI4" s="86"/>
+      <c r="AJ4" s="86"/>
+      <c r="AK4" s="86"/>
+      <c r="AL4" s="86"/>
+      <c r="AM4" s="86"/>
+      <c r="AN4" s="87"/>
+    </row>
+    <row r="5" spans="1:40" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="77"/>
+      <c r="B5" s="24" t="s">
+        <v>29</v>
+      </c>
+      <c r="C5" s="78">
+        <v>0</v>
+      </c>
+      <c r="D5" s="74"/>
+      <c r="E5" s="40" t="s">
+        <v>43</v>
+      </c>
+      <c r="F5" s="29"/>
+      <c r="G5" s="74">
+        <v>0</v>
+      </c>
+      <c r="H5" s="74"/>
+      <c r="I5" s="74"/>
+      <c r="J5" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="F4">
-        <v>0</v>
-      </c>
-      <c r="G4" s="39" t="s">
-        <v>34</v>
-      </c>
-      <c r="H4" s="41">
-        <v>0</v>
-      </c>
-      <c r="I4" s="39" t="s">
-        <v>35</v>
-      </c>
-      <c r="J4" s="41">
-        <v>0</v>
-      </c>
-      <c r="K4" s="39" t="s">
-        <v>36</v>
-      </c>
-      <c r="L4" s="53" t="s">
-        <v>40</v>
-      </c>
-      <c r="M4" s="54"/>
-      <c r="N4" s="7" t="s">
+      <c r="K5" s="30"/>
+      <c r="L5" s="78">
+        <v>0</v>
+      </c>
+      <c r="M5" s="74"/>
+      <c r="N5" s="40" t="s">
+        <v>43</v>
+      </c>
+      <c r="O5" s="29"/>
+      <c r="P5" s="74">
+        <v>0</v>
+      </c>
+      <c r="Q5" s="74"/>
+      <c r="R5" s="74"/>
+      <c r="S5" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="O4" s="41">
-        <v>0</v>
-      </c>
-      <c r="P4" s="39" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q4" s="41">
-        <v>0</v>
-      </c>
-      <c r="R4" s="39" t="s">
-        <v>35</v>
-      </c>
-      <c r="S4" s="41">
-        <v>0</v>
-      </c>
-      <c r="T4" s="42" t="s">
-        <v>36</v>
-      </c>
-      <c r="U4" s="52" t="s">
-        <v>42</v>
-      </c>
-      <c r="V4" s="27" t="s">
-        <v>31</v>
-      </c>
-      <c r="W4" s="53" t="s">
-        <v>40</v>
-      </c>
-      <c r="X4" s="54"/>
-      <c r="Y4" s="2" t="s">
+      <c r="T5" s="30"/>
+      <c r="U5" s="77"/>
+      <c r="V5" s="24" t="s">
+        <v>29</v>
+      </c>
+      <c r="W5" s="78">
+        <v>0</v>
+      </c>
+      <c r="X5" s="74"/>
+      <c r="Y5" s="40" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z5" s="29"/>
+      <c r="AA5" s="74">
+        <v>0</v>
+      </c>
+      <c r="AB5" s="74"/>
+      <c r="AC5" s="74"/>
+      <c r="AD5" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="Z4">
-        <v>0</v>
-      </c>
-      <c r="AA4" s="39" t="s">
-        <v>34</v>
-      </c>
-      <c r="AB4" s="41">
-        <v>0</v>
-      </c>
-      <c r="AC4" s="39" t="s">
-        <v>35</v>
-      </c>
-      <c r="AD4" s="41">
-        <v>0</v>
-      </c>
-      <c r="AE4" s="39" t="s">
-        <v>36</v>
-      </c>
-      <c r="AF4" s="60" t="s">
-        <v>39</v>
-      </c>
-      <c r="AG4" s="61"/>
-      <c r="AH4" s="61"/>
-      <c r="AI4" s="61"/>
-      <c r="AJ4" s="61"/>
-      <c r="AK4" s="61"/>
-      <c r="AL4" s="61"/>
-      <c r="AM4" s="61"/>
-      <c r="AN4" s="62"/>
-    </row>
-    <row r="5" spans="1:40" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="52"/>
-      <c r="B5" s="24" t="s">
-        <v>30</v>
-      </c>
-      <c r="C5" s="55">
-        <v>0</v>
-      </c>
-      <c r="D5" s="56"/>
-      <c r="E5" s="40" t="s">
-        <v>44</v>
-      </c>
-      <c r="F5" s="29"/>
-      <c r="G5" s="56">
-        <v>0</v>
-      </c>
-      <c r="H5" s="56"/>
-      <c r="I5" s="56"/>
-      <c r="J5" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="K5" s="30"/>
-      <c r="L5" s="55">
-        <v>0</v>
-      </c>
-      <c r="M5" s="56"/>
-      <c r="N5" s="40" t="s">
-        <v>44</v>
-      </c>
-      <c r="O5" s="29"/>
-      <c r="P5" s="56">
-        <v>0</v>
-      </c>
-      <c r="Q5" s="56"/>
-      <c r="R5" s="56"/>
-      <c r="S5" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="T5" s="30"/>
-      <c r="U5" s="52"/>
-      <c r="V5" s="24" t="s">
-        <v>30</v>
-      </c>
-      <c r="W5" s="55">
-        <v>0</v>
-      </c>
-      <c r="X5" s="56"/>
-      <c r="Y5" s="40" t="s">
-        <v>44</v>
-      </c>
-      <c r="Z5" s="29"/>
-      <c r="AA5" s="56">
-        <v>0</v>
-      </c>
-      <c r="AB5" s="56"/>
-      <c r="AC5" s="56"/>
-      <c r="AD5" s="5" t="s">
-        <v>38</v>
-      </c>
       <c r="AE5" s="30"/>
-      <c r="AF5" s="63"/>
-      <c r="AG5" s="64"/>
-      <c r="AH5" s="64"/>
-      <c r="AI5" s="64"/>
-      <c r="AJ5" s="64"/>
-      <c r="AK5" s="64"/>
-      <c r="AL5" s="64"/>
-      <c r="AM5" s="64"/>
-      <c r="AN5" s="65"/>
+      <c r="AF5" s="88"/>
+      <c r="AG5" s="89"/>
+      <c r="AH5" s="89"/>
+      <c r="AI5" s="89"/>
+      <c r="AJ5" s="89"/>
+      <c r="AK5" s="89"/>
+      <c r="AL5" s="89"/>
+      <c r="AM5" s="89"/>
+      <c r="AN5" s="90"/>
     </row>
     <row r="6" spans="1:40" x14ac:dyDescent="0.25">
-      <c r="A6" s="52"/>
+      <c r="A6" s="77"/>
       <c r="B6" s="23" t="s">
         <v>10</v>
       </c>
@@ -5479,19 +5479,19 @@
         <v>35.799999999999997</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E6" s="3">
         <v>70.2</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G6" s="3">
         <v>3.9</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I6" s="2" t="s">
         <v>11</v>
@@ -5506,19 +5506,19 @@
         <v>26</v>
       </c>
       <c r="M6" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="N6" s="3">
         <v>50.6</v>
       </c>
       <c r="O6" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="P6" s="3">
         <v>1.34</v>
       </c>
       <c r="Q6" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="R6" s="2" t="s">
         <v>11</v>
@@ -5529,7 +5529,7 @@
       <c r="T6" s="21" t="s">
         <v>5</v>
       </c>
-      <c r="U6" s="52"/>
+      <c r="U6" s="77"/>
       <c r="V6" s="23" t="s">
         <v>10</v>
       </c>
@@ -5537,19 +5537,19 @@
         <v>19</v>
       </c>
       <c r="X6" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="Y6" s="3">
         <v>37.299999999999997</v>
       </c>
       <c r="Z6" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AA6" s="3">
         <v>0.996</v>
       </c>
       <c r="AB6" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AC6" s="2" t="s">
         <v>11</v>
@@ -5560,18 +5560,18 @@
       <c r="AE6" s="21" t="s">
         <v>5</v>
       </c>
-      <c r="AF6" s="63"/>
-      <c r="AG6" s="64"/>
-      <c r="AH6" s="64"/>
-      <c r="AI6" s="64"/>
-      <c r="AJ6" s="64"/>
-      <c r="AK6" s="64"/>
-      <c r="AL6" s="64"/>
-      <c r="AM6" s="64"/>
-      <c r="AN6" s="65"/>
+      <c r="AF6" s="88"/>
+      <c r="AG6" s="89"/>
+      <c r="AH6" s="89"/>
+      <c r="AI6" s="89"/>
+      <c r="AJ6" s="89"/>
+      <c r="AK6" s="89"/>
+      <c r="AL6" s="89"/>
+      <c r="AM6" s="89"/>
+      <c r="AN6" s="90"/>
     </row>
     <row r="7" spans="1:40" x14ac:dyDescent="0.25">
-      <c r="A7" s="52"/>
+      <c r="A7" s="77"/>
       <c r="B7" s="23" t="s">
         <v>8</v>
       </c>
@@ -5579,7 +5579,7 @@
         <v>125</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I7" s="2" t="s">
         <v>11</v>
@@ -5594,7 +5594,7 @@
         <v>122.2</v>
       </c>
       <c r="M7" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="R7" s="2" t="s">
         <v>11</v>
@@ -5605,7 +5605,7 @@
       <c r="T7" s="21" t="s">
         <v>5</v>
       </c>
-      <c r="U7" s="52"/>
+      <c r="U7" s="77"/>
       <c r="V7" s="23" t="s">
         <v>8</v>
       </c>
@@ -5613,7 +5613,7 @@
         <v>107</v>
       </c>
       <c r="X7" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AC7" s="2" t="s">
         <v>11</v>
@@ -5624,35 +5624,35 @@
       <c r="AE7" s="21" t="s">
         <v>5</v>
       </c>
-      <c r="AF7" s="63"/>
-      <c r="AG7" s="64"/>
-      <c r="AH7" s="64"/>
-      <c r="AI7" s="64"/>
-      <c r="AJ7" s="64"/>
-      <c r="AK7" s="64"/>
-      <c r="AL7" s="64"/>
-      <c r="AM7" s="64"/>
-      <c r="AN7" s="65"/>
+      <c r="AF7" s="88"/>
+      <c r="AG7" s="89"/>
+      <c r="AH7" s="89"/>
+      <c r="AI7" s="89"/>
+      <c r="AJ7" s="89"/>
+      <c r="AK7" s="89"/>
+      <c r="AL7" s="89"/>
+      <c r="AM7" s="89"/>
+      <c r="AN7" s="90"/>
     </row>
     <row r="8" spans="1:40" x14ac:dyDescent="0.25">
-      <c r="A8" s="52"/>
+      <c r="A8" s="77"/>
       <c r="B8" s="23" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C8" s="33">
         <v>8.02</v>
       </c>
       <c r="D8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E8" s="28" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G8" s="3">
         <v>125</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I8" s="2" t="s">
         <v>11</v>
@@ -5667,16 +5667,16 @@
         <v>8.18</v>
       </c>
       <c r="M8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="N8" s="28" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="P8" s="3">
         <v>122</v>
       </c>
       <c r="Q8" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="R8" s="2" t="s">
         <v>11</v>
@@ -5687,24 +5687,24 @@
       <c r="T8" s="21" t="s">
         <v>5</v>
       </c>
-      <c r="U8" s="52"/>
+      <c r="U8" s="77"/>
       <c r="V8" s="23" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="W8" s="33">
         <v>8.86</v>
       </c>
       <c r="X8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y8" s="28" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AA8" s="3">
         <v>107</v>
       </c>
       <c r="AB8" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AC8" s="2" t="s">
         <v>11</v>
@@ -5715,18 +5715,18 @@
       <c r="AE8" s="21" t="s">
         <v>5</v>
       </c>
-      <c r="AF8" s="63"/>
-      <c r="AG8" s="64"/>
-      <c r="AH8" s="64"/>
-      <c r="AI8" s="64"/>
-      <c r="AJ8" s="64"/>
-      <c r="AK8" s="64"/>
-      <c r="AL8" s="64"/>
-      <c r="AM8" s="64"/>
-      <c r="AN8" s="65"/>
+      <c r="AF8" s="88"/>
+      <c r="AG8" s="89"/>
+      <c r="AH8" s="89"/>
+      <c r="AI8" s="89"/>
+      <c r="AJ8" s="89"/>
+      <c r="AK8" s="89"/>
+      <c r="AL8" s="89"/>
+      <c r="AM8" s="89"/>
+      <c r="AN8" s="90"/>
     </row>
     <row r="9" spans="1:40" x14ac:dyDescent="0.25">
-      <c r="A9" s="52"/>
+      <c r="A9" s="77"/>
       <c r="B9" s="23" t="s">
         <v>9</v>
       </c>
@@ -5754,7 +5754,7 @@
       <c r="T9" s="21" t="s">
         <v>5</v>
       </c>
-      <c r="U9" s="52"/>
+      <c r="U9" s="77"/>
       <c r="V9" s="23" t="s">
         <v>9</v>
       </c>
@@ -5770,26 +5770,26 @@
       <c r="AE9" s="21" t="s">
         <v>5</v>
       </c>
-      <c r="AF9" s="63"/>
-      <c r="AG9" s="64"/>
-      <c r="AH9" s="64"/>
-      <c r="AI9" s="64"/>
-      <c r="AJ9" s="64"/>
-      <c r="AK9" s="64"/>
-      <c r="AL9" s="64"/>
-      <c r="AM9" s="64"/>
-      <c r="AN9" s="65"/>
+      <c r="AF9" s="88"/>
+      <c r="AG9" s="89"/>
+      <c r="AH9" s="89"/>
+      <c r="AI9" s="89"/>
+      <c r="AJ9" s="89"/>
+      <c r="AK9" s="89"/>
+      <c r="AL9" s="89"/>
+      <c r="AM9" s="89"/>
+      <c r="AN9" s="90"/>
     </row>
     <row r="10" spans="1:40" x14ac:dyDescent="0.25">
-      <c r="A10" s="52"/>
+      <c r="A10" s="77"/>
       <c r="B10" s="24" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C10" s="34">
         <v>355</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E10" s="6"/>
       <c r="F10" s="5"/>
@@ -5808,7 +5808,7 @@
         <v>242</v>
       </c>
       <c r="M10" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="N10" s="6"/>
       <c r="O10" s="5"/>
@@ -5823,15 +5823,15 @@
       <c r="T10" s="22" t="s">
         <v>5</v>
       </c>
-      <c r="U10" s="52"/>
+      <c r="U10" s="77"/>
       <c r="V10" s="24" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="W10" s="34">
         <v>299</v>
       </c>
       <c r="X10" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Y10" s="6"/>
       <c r="Z10" s="5"/>
@@ -5846,188 +5846,188 @@
       <c r="AE10" s="22" t="s">
         <v>5</v>
       </c>
-      <c r="AF10" s="66"/>
-      <c r="AG10" s="67"/>
-      <c r="AH10" s="67"/>
-      <c r="AI10" s="67"/>
-      <c r="AJ10" s="67"/>
-      <c r="AK10" s="67"/>
-      <c r="AL10" s="67"/>
-      <c r="AM10" s="67"/>
-      <c r="AN10" s="68"/>
+      <c r="AF10" s="91"/>
+      <c r="AG10" s="92"/>
+      <c r="AH10" s="92"/>
+      <c r="AI10" s="92"/>
+      <c r="AJ10" s="92"/>
+      <c r="AK10" s="92"/>
+      <c r="AL10" s="92"/>
+      <c r="AM10" s="92"/>
+      <c r="AN10" s="93"/>
     </row>
     <row r="11" spans="1:40" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="52" t="s">
-        <v>45</v>
+      <c r="A11" s="77" t="s">
+        <v>44</v>
       </c>
       <c r="B11" s="27" t="s">
-        <v>31</v>
-      </c>
-      <c r="C11" s="53" t="s">
-        <v>40</v>
-      </c>
-      <c r="D11" s="54"/>
+        <v>30</v>
+      </c>
+      <c r="C11" s="75" t="s">
+        <v>39</v>
+      </c>
+      <c r="D11" s="76"/>
       <c r="E11" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="F11" s="41">
+        <v>0</v>
+      </c>
+      <c r="G11" s="39" t="s">
+        <v>33</v>
+      </c>
+      <c r="H11" s="41">
+        <v>0</v>
+      </c>
+      <c r="I11" s="39" t="s">
+        <v>34</v>
+      </c>
+      <c r="J11" s="41">
+        <v>0</v>
+      </c>
+      <c r="K11" s="39" t="s">
+        <v>35</v>
+      </c>
+      <c r="L11" s="75" t="s">
+        <v>39</v>
+      </c>
+      <c r="M11" s="76"/>
+      <c r="N11" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="O11" s="41">
+        <v>0</v>
+      </c>
+      <c r="P11" s="39" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q11" s="41">
+        <v>0</v>
+      </c>
+      <c r="R11" s="39" t="s">
+        <v>34</v>
+      </c>
+      <c r="S11" s="41">
+        <v>0</v>
+      </c>
+      <c r="T11" s="39" t="s">
+        <v>35</v>
+      </c>
+      <c r="U11" s="77" t="s">
+        <v>44</v>
+      </c>
+      <c r="V11" s="27" t="s">
+        <v>30</v>
+      </c>
+      <c r="W11" s="75" t="s">
+        <v>39</v>
+      </c>
+      <c r="X11" s="76"/>
+      <c r="Y11" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="Z11" s="41">
+        <v>0</v>
+      </c>
+      <c r="AA11" s="39" t="s">
+        <v>33</v>
+      </c>
+      <c r="AB11" s="41">
+        <v>0</v>
+      </c>
+      <c r="AC11" s="39" t="s">
+        <v>34</v>
+      </c>
+      <c r="AD11" s="41">
+        <v>0</v>
+      </c>
+      <c r="AE11" s="39" t="s">
+        <v>35</v>
+      </c>
+      <c r="AF11" s="85" t="s">
+        <v>38</v>
+      </c>
+      <c r="AG11" s="86"/>
+      <c r="AH11" s="86"/>
+      <c r="AI11" s="86"/>
+      <c r="AJ11" s="86"/>
+      <c r="AK11" s="86"/>
+      <c r="AL11" s="86"/>
+      <c r="AM11" s="86"/>
+      <c r="AN11" s="87"/>
+    </row>
+    <row r="12" spans="1:40" x14ac:dyDescent="0.25">
+      <c r="A12" s="77"/>
+      <c r="B12" s="24" t="s">
+        <v>29</v>
+      </c>
+      <c r="C12" s="78">
+        <v>0</v>
+      </c>
+      <c r="D12" s="74"/>
+      <c r="E12" s="40" t="s">
+        <v>43</v>
+      </c>
+      <c r="F12" s="29"/>
+      <c r="G12" s="74">
+        <v>0</v>
+      </c>
+      <c r="H12" s="74"/>
+      <c r="I12" s="74"/>
+      <c r="J12" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="F11" s="41">
-        <v>0</v>
-      </c>
-      <c r="G11" s="39" t="s">
-        <v>34</v>
-      </c>
-      <c r="H11" s="41">
-        <v>0</v>
-      </c>
-      <c r="I11" s="39" t="s">
-        <v>35</v>
-      </c>
-      <c r="J11" s="41">
-        <v>0</v>
-      </c>
-      <c r="K11" s="39" t="s">
-        <v>36</v>
-      </c>
-      <c r="L11" s="53" t="s">
-        <v>40</v>
-      </c>
-      <c r="M11" s="54"/>
-      <c r="N11" s="7" t="s">
+      <c r="K12" s="30"/>
+      <c r="L12" s="78">
+        <v>0</v>
+      </c>
+      <c r="M12" s="74"/>
+      <c r="N12" s="40" t="s">
+        <v>43</v>
+      </c>
+      <c r="O12" s="29"/>
+      <c r="P12" s="74">
+        <v>0</v>
+      </c>
+      <c r="Q12" s="74"/>
+      <c r="R12" s="74"/>
+      <c r="S12" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="O11" s="41">
-        <v>0</v>
-      </c>
-      <c r="P11" s="39" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q11" s="41">
-        <v>0</v>
-      </c>
-      <c r="R11" s="39" t="s">
-        <v>35</v>
-      </c>
-      <c r="S11" s="41">
-        <v>0</v>
-      </c>
-      <c r="T11" s="39" t="s">
-        <v>36</v>
-      </c>
-      <c r="U11" s="52" t="s">
-        <v>45</v>
-      </c>
-      <c r="V11" s="27" t="s">
-        <v>31</v>
-      </c>
-      <c r="W11" s="53" t="s">
-        <v>40</v>
-      </c>
-      <c r="X11" s="54"/>
-      <c r="Y11" s="7" t="s">
+      <c r="T12" s="30"/>
+      <c r="U12" s="77"/>
+      <c r="V12" s="24" t="s">
+        <v>29</v>
+      </c>
+      <c r="W12" s="78">
+        <v>0</v>
+      </c>
+      <c r="X12" s="74"/>
+      <c r="Y12" s="40" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z12" s="29"/>
+      <c r="AA12" s="74">
+        <v>0</v>
+      </c>
+      <c r="AB12" s="74"/>
+      <c r="AC12" s="74"/>
+      <c r="AD12" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="Z11" s="41">
-        <v>0</v>
-      </c>
-      <c r="AA11" s="39" t="s">
-        <v>34</v>
-      </c>
-      <c r="AB11" s="41">
-        <v>0</v>
-      </c>
-      <c r="AC11" s="39" t="s">
-        <v>35</v>
-      </c>
-      <c r="AD11" s="41">
-        <v>0</v>
-      </c>
-      <c r="AE11" s="39" t="s">
-        <v>36</v>
-      </c>
-      <c r="AF11" s="60" t="s">
-        <v>39</v>
-      </c>
-      <c r="AG11" s="61"/>
-      <c r="AH11" s="61"/>
-      <c r="AI11" s="61"/>
-      <c r="AJ11" s="61"/>
-      <c r="AK11" s="61"/>
-      <c r="AL11" s="61"/>
-      <c r="AM11" s="61"/>
-      <c r="AN11" s="62"/>
-    </row>
-    <row r="12" spans="1:40" x14ac:dyDescent="0.25">
-      <c r="A12" s="52"/>
-      <c r="B12" s="24" t="s">
-        <v>30</v>
-      </c>
-      <c r="C12" s="55">
-        <v>0</v>
-      </c>
-      <c r="D12" s="56"/>
-      <c r="E12" s="40" t="s">
-        <v>44</v>
-      </c>
-      <c r="F12" s="29"/>
-      <c r="G12" s="56">
-        <v>0</v>
-      </c>
-      <c r="H12" s="56"/>
-      <c r="I12" s="56"/>
-      <c r="J12" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="K12" s="30"/>
-      <c r="L12" s="55">
-        <v>0</v>
-      </c>
-      <c r="M12" s="56"/>
-      <c r="N12" s="40" t="s">
-        <v>44</v>
-      </c>
-      <c r="O12" s="29"/>
-      <c r="P12" s="56">
-        <v>0</v>
-      </c>
-      <c r="Q12" s="56"/>
-      <c r="R12" s="56"/>
-      <c r="S12" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="T12" s="30"/>
-      <c r="U12" s="52"/>
-      <c r="V12" s="24" t="s">
-        <v>30</v>
-      </c>
-      <c r="W12" s="55">
-        <v>0</v>
-      </c>
-      <c r="X12" s="56"/>
-      <c r="Y12" s="40" t="s">
-        <v>44</v>
-      </c>
-      <c r="Z12" s="29"/>
-      <c r="AA12" s="56">
-        <v>0</v>
-      </c>
-      <c r="AB12" s="56"/>
-      <c r="AC12" s="56"/>
-      <c r="AD12" s="5" t="s">
-        <v>38</v>
-      </c>
       <c r="AE12" s="30"/>
-      <c r="AF12" s="63"/>
-      <c r="AG12" s="64"/>
-      <c r="AH12" s="64"/>
-      <c r="AI12" s="64"/>
-      <c r="AJ12" s="64"/>
-      <c r="AK12" s="64"/>
-      <c r="AL12" s="64"/>
-      <c r="AM12" s="64"/>
-      <c r="AN12" s="65"/>
+      <c r="AF12" s="88"/>
+      <c r="AG12" s="89"/>
+      <c r="AH12" s="89"/>
+      <c r="AI12" s="89"/>
+      <c r="AJ12" s="89"/>
+      <c r="AK12" s="89"/>
+      <c r="AL12" s="89"/>
+      <c r="AM12" s="89"/>
+      <c r="AN12" s="90"/>
     </row>
     <row r="13" spans="1:40" x14ac:dyDescent="0.25">
-      <c r="A13" s="52"/>
+      <c r="A13" s="77"/>
       <c r="B13" s="23" t="s">
         <v>10</v>
       </c>
@@ -6035,19 +6035,19 @@
         <v>145.30000000000001</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E13" s="3">
         <v>287</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G13" s="3">
         <v>11.19</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I13" s="2" t="s">
         <v>11</v>
@@ -6062,19 +6062,19 @@
         <v>106.3</v>
       </c>
       <c r="M13" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="N13" s="3">
         <v>211</v>
       </c>
       <c r="O13" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="P13" s="3">
         <v>8.64</v>
       </c>
       <c r="Q13" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="R13" s="2" t="s">
         <v>11</v>
@@ -6085,7 +6085,7 @@
       <c r="T13" s="21" t="s">
         <v>5</v>
       </c>
-      <c r="U13" s="52"/>
+      <c r="U13" s="77"/>
       <c r="V13" s="23" t="s">
         <v>10</v>
       </c>
@@ -6093,19 +6093,19 @@
         <v>45.5</v>
       </c>
       <c r="X13" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="Y13" s="3">
         <v>89.3</v>
       </c>
       <c r="Z13" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AA13" s="3">
         <v>3.64</v>
       </c>
       <c r="AB13" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AC13" s="2" t="s">
         <v>11</v>
@@ -6116,18 +6116,18 @@
       <c r="AE13" s="21" t="s">
         <v>5</v>
       </c>
-      <c r="AF13" s="63"/>
-      <c r="AG13" s="64"/>
-      <c r="AH13" s="64"/>
-      <c r="AI13" s="64"/>
-      <c r="AJ13" s="64"/>
-      <c r="AK13" s="64"/>
-      <c r="AL13" s="64"/>
-      <c r="AM13" s="64"/>
-      <c r="AN13" s="65"/>
+      <c r="AF13" s="88"/>
+      <c r="AG13" s="89"/>
+      <c r="AH13" s="89"/>
+      <c r="AI13" s="89"/>
+      <c r="AJ13" s="89"/>
+      <c r="AK13" s="89"/>
+      <c r="AL13" s="89"/>
+      <c r="AM13" s="89"/>
+      <c r="AN13" s="90"/>
     </row>
     <row r="14" spans="1:40" x14ac:dyDescent="0.25">
-      <c r="A14" s="52"/>
+      <c r="A14" s="77"/>
       <c r="B14" s="23" t="s">
         <v>8</v>
       </c>
@@ -6135,7 +6135,7 @@
         <v>136.19999999999999</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I14" s="2" t="s">
         <v>11</v>
@@ -6150,7 +6150,7 @@
         <v>76</v>
       </c>
       <c r="M14" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="R14" s="2" t="s">
         <v>11</v>
@@ -6161,7 +6161,7 @@
       <c r="T14" s="21" t="s">
         <v>5</v>
       </c>
-      <c r="U14" s="52"/>
+      <c r="U14" s="77"/>
       <c r="V14" s="23" t="s">
         <v>8</v>
       </c>
@@ -6169,7 +6169,7 @@
         <v>143.4</v>
       </c>
       <c r="X14" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AC14" s="2" t="s">
         <v>11</v>
@@ -6180,35 +6180,35 @@
       <c r="AE14" s="21" t="s">
         <v>5</v>
       </c>
-      <c r="AF14" s="63"/>
-      <c r="AG14" s="64"/>
-      <c r="AH14" s="64"/>
-      <c r="AI14" s="64"/>
-      <c r="AJ14" s="64"/>
-      <c r="AK14" s="64"/>
-      <c r="AL14" s="64"/>
-      <c r="AM14" s="64"/>
-      <c r="AN14" s="65"/>
+      <c r="AF14" s="88"/>
+      <c r="AG14" s="89"/>
+      <c r="AH14" s="89"/>
+      <c r="AI14" s="89"/>
+      <c r="AJ14" s="89"/>
+      <c r="AK14" s="89"/>
+      <c r="AL14" s="89"/>
+      <c r="AM14" s="89"/>
+      <c r="AN14" s="90"/>
     </row>
     <row r="15" spans="1:40" x14ac:dyDescent="0.25">
-      <c r="A15" s="52"/>
+      <c r="A15" s="77"/>
       <c r="B15" s="23" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C15" s="33">
         <v>7.34</v>
       </c>
       <c r="D15" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E15" s="28" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G15" s="3">
         <v>136</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I15" s="2" t="s">
         <v>11</v>
@@ -6223,16 +6223,16 @@
         <v>13.03</v>
       </c>
       <c r="M15" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="N15" s="28" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="P15" s="3">
         <v>77</v>
       </c>
       <c r="Q15" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="R15" s="2" t="s">
         <v>11</v>
@@ -6243,24 +6243,24 @@
       <c r="T15" s="21" t="s">
         <v>5</v>
       </c>
-      <c r="U15" s="52"/>
+      <c r="U15" s="77"/>
       <c r="V15" s="23" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="W15" s="33">
         <v>6.96</v>
       </c>
       <c r="X15" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y15" s="28" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AA15" s="3">
         <v>143</v>
       </c>
       <c r="AB15" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AC15" s="2" t="s">
         <v>11</v>
@@ -6271,18 +6271,18 @@
       <c r="AE15" s="21" t="s">
         <v>5</v>
       </c>
-      <c r="AF15" s="63"/>
-      <c r="AG15" s="64"/>
-      <c r="AH15" s="64"/>
-      <c r="AI15" s="64"/>
-      <c r="AJ15" s="64"/>
-      <c r="AK15" s="64"/>
-      <c r="AL15" s="64"/>
-      <c r="AM15" s="64"/>
-      <c r="AN15" s="65"/>
+      <c r="AF15" s="88"/>
+      <c r="AG15" s="89"/>
+      <c r="AH15" s="89"/>
+      <c r="AI15" s="89"/>
+      <c r="AJ15" s="89"/>
+      <c r="AK15" s="89"/>
+      <c r="AL15" s="89"/>
+      <c r="AM15" s="89"/>
+      <c r="AN15" s="90"/>
     </row>
     <row r="16" spans="1:40" x14ac:dyDescent="0.25">
-      <c r="A16" s="52"/>
+      <c r="A16" s="77"/>
       <c r="B16" s="23" t="s">
         <v>9</v>
       </c>
@@ -6310,7 +6310,7 @@
       <c r="T16" s="21" t="s">
         <v>5</v>
       </c>
-      <c r="U16" s="52"/>
+      <c r="U16" s="77"/>
       <c r="V16" s="23" t="s">
         <v>9</v>
       </c>
@@ -6326,26 +6326,26 @@
       <c r="AE16" s="21" t="s">
         <v>5</v>
       </c>
-      <c r="AF16" s="63"/>
-      <c r="AG16" s="64"/>
-      <c r="AH16" s="64"/>
-      <c r="AI16" s="64"/>
-      <c r="AJ16" s="64"/>
-      <c r="AK16" s="64"/>
-      <c r="AL16" s="64"/>
-      <c r="AM16" s="64"/>
-      <c r="AN16" s="65"/>
+      <c r="AF16" s="88"/>
+      <c r="AG16" s="89"/>
+      <c r="AH16" s="89"/>
+      <c r="AI16" s="89"/>
+      <c r="AJ16" s="89"/>
+      <c r="AK16" s="89"/>
+      <c r="AL16" s="89"/>
+      <c r="AM16" s="89"/>
+      <c r="AN16" s="90"/>
     </row>
     <row r="17" spans="1:40" x14ac:dyDescent="0.25">
-      <c r="A17" s="52"/>
+      <c r="A17" s="77"/>
       <c r="B17" s="24" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C17" s="34">
         <v>314</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E17" s="6"/>
       <c r="F17" s="5"/>
@@ -6364,7 +6364,7 @@
         <v>364.4</v>
       </c>
       <c r="M17" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="N17" s="6"/>
       <c r="O17" s="5"/>
@@ -6379,15 +6379,15 @@
       <c r="T17" s="22" t="s">
         <v>5</v>
       </c>
-      <c r="U17" s="52"/>
+      <c r="U17" s="77"/>
       <c r="V17" s="24" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="W17" s="34">
         <v>298.8</v>
       </c>
       <c r="X17" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Y17" s="6"/>
       <c r="Z17" s="5"/>
@@ -6402,188 +6402,188 @@
       <c r="AE17" s="22" t="s">
         <v>5</v>
       </c>
-      <c r="AF17" s="66"/>
-      <c r="AG17" s="67"/>
-      <c r="AH17" s="67"/>
-      <c r="AI17" s="67"/>
-      <c r="AJ17" s="67"/>
-      <c r="AK17" s="67"/>
-      <c r="AL17" s="67"/>
-      <c r="AM17" s="67"/>
-      <c r="AN17" s="68"/>
+      <c r="AF17" s="91"/>
+      <c r="AG17" s="92"/>
+      <c r="AH17" s="92"/>
+      <c r="AI17" s="92"/>
+      <c r="AJ17" s="92"/>
+      <c r="AK17" s="92"/>
+      <c r="AL17" s="92"/>
+      <c r="AM17" s="92"/>
+      <c r="AN17" s="93"/>
     </row>
     <row r="18" spans="1:40" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="52" t="s">
-        <v>56</v>
+      <c r="A18" s="77" t="s">
+        <v>55</v>
       </c>
       <c r="B18" s="27" t="s">
-        <v>31</v>
-      </c>
-      <c r="C18" s="53" t="s">
-        <v>40</v>
-      </c>
-      <c r="D18" s="54"/>
+        <v>30</v>
+      </c>
+      <c r="C18" s="75" t="s">
+        <v>39</v>
+      </c>
+      <c r="D18" s="76"/>
       <c r="E18" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="F18" s="41">
+        <v>0</v>
+      </c>
+      <c r="G18" s="39" t="s">
+        <v>33</v>
+      </c>
+      <c r="H18" s="41">
+        <v>0</v>
+      </c>
+      <c r="I18" s="39" t="s">
+        <v>34</v>
+      </c>
+      <c r="J18" s="41">
+        <v>0</v>
+      </c>
+      <c r="K18" s="39" t="s">
+        <v>35</v>
+      </c>
+      <c r="L18" s="75" t="s">
+        <v>39</v>
+      </c>
+      <c r="M18" s="76"/>
+      <c r="N18" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="O18" s="41">
+        <v>0</v>
+      </c>
+      <c r="P18" s="39" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q18" s="41">
+        <v>0</v>
+      </c>
+      <c r="R18" s="39" t="s">
+        <v>34</v>
+      </c>
+      <c r="S18" s="41">
+        <v>0</v>
+      </c>
+      <c r="T18" s="39" t="s">
+        <v>35</v>
+      </c>
+      <c r="U18" s="77" t="s">
+        <v>55</v>
+      </c>
+      <c r="V18" s="27" t="s">
+        <v>30</v>
+      </c>
+      <c r="W18" s="75" t="s">
+        <v>39</v>
+      </c>
+      <c r="X18" s="76"/>
+      <c r="Y18" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="Z18" s="41">
+        <v>0</v>
+      </c>
+      <c r="AA18" s="39" t="s">
+        <v>33</v>
+      </c>
+      <c r="AB18" s="41">
+        <v>0</v>
+      </c>
+      <c r="AC18" s="39" t="s">
+        <v>34</v>
+      </c>
+      <c r="AD18" s="41">
+        <v>0</v>
+      </c>
+      <c r="AE18" s="39" t="s">
+        <v>35</v>
+      </c>
+      <c r="AF18" s="85" t="s">
+        <v>38</v>
+      </c>
+      <c r="AG18" s="86"/>
+      <c r="AH18" s="86"/>
+      <c r="AI18" s="86"/>
+      <c r="AJ18" s="86"/>
+      <c r="AK18" s="86"/>
+      <c r="AL18" s="86"/>
+      <c r="AM18" s="86"/>
+      <c r="AN18" s="87"/>
+    </row>
+    <row r="19" spans="1:40" x14ac:dyDescent="0.25">
+      <c r="A19" s="77"/>
+      <c r="B19" s="24" t="s">
+        <v>29</v>
+      </c>
+      <c r="C19" s="78">
+        <v>0</v>
+      </c>
+      <c r="D19" s="74"/>
+      <c r="E19" s="40" t="s">
+        <v>43</v>
+      </c>
+      <c r="F19" s="29"/>
+      <c r="G19" s="74">
+        <v>0</v>
+      </c>
+      <c r="H19" s="74"/>
+      <c r="I19" s="74"/>
+      <c r="J19" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="F18" s="41">
-        <v>0</v>
-      </c>
-      <c r="G18" s="39" t="s">
-        <v>34</v>
-      </c>
-      <c r="H18" s="41">
-        <v>0</v>
-      </c>
-      <c r="I18" s="39" t="s">
-        <v>35</v>
-      </c>
-      <c r="J18" s="41">
-        <v>0</v>
-      </c>
-      <c r="K18" s="39" t="s">
-        <v>36</v>
-      </c>
-      <c r="L18" s="53" t="s">
-        <v>40</v>
-      </c>
-      <c r="M18" s="54"/>
-      <c r="N18" s="7" t="s">
+      <c r="K19" s="30"/>
+      <c r="L19" s="78">
+        <v>0</v>
+      </c>
+      <c r="M19" s="74"/>
+      <c r="N19" s="40" t="s">
+        <v>43</v>
+      </c>
+      <c r="O19" s="29"/>
+      <c r="P19" s="74">
+        <v>0</v>
+      </c>
+      <c r="Q19" s="74"/>
+      <c r="R19" s="74"/>
+      <c r="S19" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="O18" s="41">
-        <v>0</v>
-      </c>
-      <c r="P18" s="39" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q18" s="41">
-        <v>0</v>
-      </c>
-      <c r="R18" s="39" t="s">
-        <v>35</v>
-      </c>
-      <c r="S18" s="41">
-        <v>0</v>
-      </c>
-      <c r="T18" s="39" t="s">
-        <v>36</v>
-      </c>
-      <c r="U18" s="52" t="s">
-        <v>56</v>
-      </c>
-      <c r="V18" s="27" t="s">
-        <v>31</v>
-      </c>
-      <c r="W18" s="53" t="s">
-        <v>40</v>
-      </c>
-      <c r="X18" s="54"/>
-      <c r="Y18" s="7" t="s">
+      <c r="T19" s="30"/>
+      <c r="U19" s="77"/>
+      <c r="V19" s="24" t="s">
+        <v>29</v>
+      </c>
+      <c r="W19" s="78">
+        <v>0</v>
+      </c>
+      <c r="X19" s="74"/>
+      <c r="Y19" s="40" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z19" s="29"/>
+      <c r="AA19" s="74">
+        <v>0</v>
+      </c>
+      <c r="AB19" s="74"/>
+      <c r="AC19" s="74"/>
+      <c r="AD19" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="Z18" s="41">
-        <v>0</v>
-      </c>
-      <c r="AA18" s="39" t="s">
-        <v>34</v>
-      </c>
-      <c r="AB18" s="41">
-        <v>0</v>
-      </c>
-      <c r="AC18" s="39" t="s">
-        <v>35</v>
-      </c>
-      <c r="AD18" s="41">
-        <v>0</v>
-      </c>
-      <c r="AE18" s="39" t="s">
-        <v>36</v>
-      </c>
-      <c r="AF18" s="60" t="s">
-        <v>39</v>
-      </c>
-      <c r="AG18" s="61"/>
-      <c r="AH18" s="61"/>
-      <c r="AI18" s="61"/>
-      <c r="AJ18" s="61"/>
-      <c r="AK18" s="61"/>
-      <c r="AL18" s="61"/>
-      <c r="AM18" s="61"/>
-      <c r="AN18" s="62"/>
-    </row>
-    <row r="19" spans="1:40" x14ac:dyDescent="0.25">
-      <c r="A19" s="52"/>
-      <c r="B19" s="24" t="s">
-        <v>30</v>
-      </c>
-      <c r="C19" s="55">
-        <v>0</v>
-      </c>
-      <c r="D19" s="56"/>
-      <c r="E19" s="40" t="s">
-        <v>44</v>
-      </c>
-      <c r="F19" s="29"/>
-      <c r="G19" s="56">
-        <v>0</v>
-      </c>
-      <c r="H19" s="56"/>
-      <c r="I19" s="56"/>
-      <c r="J19" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="K19" s="30"/>
-      <c r="L19" s="55">
-        <v>0</v>
-      </c>
-      <c r="M19" s="56"/>
-      <c r="N19" s="40" t="s">
-        <v>44</v>
-      </c>
-      <c r="O19" s="29"/>
-      <c r="P19" s="56">
-        <v>0</v>
-      </c>
-      <c r="Q19" s="56"/>
-      <c r="R19" s="56"/>
-      <c r="S19" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="T19" s="30"/>
-      <c r="U19" s="52"/>
-      <c r="V19" s="24" t="s">
-        <v>30</v>
-      </c>
-      <c r="W19" s="55">
-        <v>0</v>
-      </c>
-      <c r="X19" s="56"/>
-      <c r="Y19" s="40" t="s">
-        <v>44</v>
-      </c>
-      <c r="Z19" s="29"/>
-      <c r="AA19" s="56">
-        <v>0</v>
-      </c>
-      <c r="AB19" s="56"/>
-      <c r="AC19" s="56"/>
-      <c r="AD19" s="5" t="s">
-        <v>38</v>
-      </c>
       <c r="AE19" s="30"/>
-      <c r="AF19" s="63"/>
-      <c r="AG19" s="64"/>
-      <c r="AH19" s="64"/>
-      <c r="AI19" s="64"/>
-      <c r="AJ19" s="64"/>
-      <c r="AK19" s="64"/>
-      <c r="AL19" s="64"/>
-      <c r="AM19" s="64"/>
-      <c r="AN19" s="65"/>
+      <c r="AF19" s="88"/>
+      <c r="AG19" s="89"/>
+      <c r="AH19" s="89"/>
+      <c r="AI19" s="89"/>
+      <c r="AJ19" s="89"/>
+      <c r="AK19" s="89"/>
+      <c r="AL19" s="89"/>
+      <c r="AM19" s="89"/>
+      <c r="AN19" s="90"/>
     </row>
     <row r="20" spans="1:40" x14ac:dyDescent="0.25">
-      <c r="A20" s="52"/>
+      <c r="A20" s="77"/>
       <c r="B20" s="23" t="s">
         <v>10</v>
       </c>
@@ -6591,19 +6591,19 @@
         <v>61</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E20" s="3">
         <v>121.7</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G20" s="3">
         <v>3.59</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I20" s="2" t="s">
         <v>11</v>
@@ -6618,19 +6618,19 @@
         <v>132.19999999999999</v>
       </c>
       <c r="M20" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="N20" s="3">
         <v>262</v>
       </c>
       <c r="O20" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="P20" s="3">
         <v>7.46</v>
       </c>
       <c r="Q20" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="R20" s="2" t="s">
         <v>11</v>
@@ -6641,7 +6641,7 @@
       <c r="T20" s="21" t="s">
         <v>5</v>
       </c>
-      <c r="U20" s="52"/>
+      <c r="U20" s="77"/>
       <c r="V20" s="23" t="s">
         <v>10</v>
       </c>
@@ -6649,19 +6649,19 @@
         <v>134.80000000000001</v>
       </c>
       <c r="X20" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="Y20" s="3">
         <v>266</v>
       </c>
       <c r="Z20" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AA20" s="3">
         <v>7.45</v>
       </c>
       <c r="AB20" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AC20" s="2" t="s">
         <v>11</v>
@@ -6672,18 +6672,18 @@
       <c r="AE20" s="21" t="s">
         <v>5</v>
       </c>
-      <c r="AF20" s="63"/>
-      <c r="AG20" s="64"/>
-      <c r="AH20" s="64"/>
-      <c r="AI20" s="64"/>
-      <c r="AJ20" s="64"/>
-      <c r="AK20" s="64"/>
-      <c r="AL20" s="64"/>
-      <c r="AM20" s="64"/>
-      <c r="AN20" s="65"/>
+      <c r="AF20" s="88"/>
+      <c r="AG20" s="89"/>
+      <c r="AH20" s="89"/>
+      <c r="AI20" s="89"/>
+      <c r="AJ20" s="89"/>
+      <c r="AK20" s="89"/>
+      <c r="AL20" s="89"/>
+      <c r="AM20" s="89"/>
+      <c r="AN20" s="90"/>
     </row>
     <row r="21" spans="1:40" x14ac:dyDescent="0.25">
-      <c r="A21" s="52"/>
+      <c r="A21" s="77"/>
       <c r="B21" s="23" t="s">
         <v>8</v>
       </c>
@@ -6691,7 +6691,7 @@
         <v>123.3</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I21" s="2" t="s">
         <v>11</v>
@@ -6706,7 +6706,7 @@
         <v>132</v>
       </c>
       <c r="M21" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="R21" s="2" t="s">
         <v>11</v>
@@ -6717,7 +6717,7 @@
       <c r="T21" s="21" t="s">
         <v>5</v>
       </c>
-      <c r="U21" s="52"/>
+      <c r="U21" s="77"/>
       <c r="V21" s="23" t="s">
         <v>8</v>
       </c>
@@ -6725,7 +6725,7 @@
         <v>100.1</v>
       </c>
       <c r="X21" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AC21" s="2" t="s">
         <v>11</v>
@@ -6736,35 +6736,35 @@
       <c r="AE21" s="21" t="s">
         <v>5</v>
       </c>
-      <c r="AF21" s="63"/>
-      <c r="AG21" s="64"/>
-      <c r="AH21" s="64"/>
-      <c r="AI21" s="64"/>
-      <c r="AJ21" s="64"/>
-      <c r="AK21" s="64"/>
-      <c r="AL21" s="64"/>
-      <c r="AM21" s="64"/>
-      <c r="AN21" s="65"/>
+      <c r="AF21" s="88"/>
+      <c r="AG21" s="89"/>
+      <c r="AH21" s="89"/>
+      <c r="AI21" s="89"/>
+      <c r="AJ21" s="89"/>
+      <c r="AK21" s="89"/>
+      <c r="AL21" s="89"/>
+      <c r="AM21" s="89"/>
+      <c r="AN21" s="90"/>
     </row>
     <row r="22" spans="1:40" x14ac:dyDescent="0.25">
-      <c r="A22" s="52"/>
+      <c r="A22" s="77"/>
       <c r="B22" s="23" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C22" s="33">
         <v>8.1</v>
       </c>
       <c r="D22" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E22" s="28" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G22" s="3">
         <v>123</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I22" s="2" t="s">
         <v>11</v>
@@ -6779,16 +6779,16 @@
         <v>7.57</v>
       </c>
       <c r="M22" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="N22" s="28" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="P22" s="3">
         <v>132</v>
       </c>
       <c r="Q22" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="R22" s="2" t="s">
         <v>11</v>
@@ -6799,24 +6799,24 @@
       <c r="T22" s="21" t="s">
         <v>5</v>
       </c>
-      <c r="U22" s="52"/>
+      <c r="U22" s="77"/>
       <c r="V22" s="23" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="W22" s="33">
         <v>10</v>
       </c>
       <c r="X22" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y22" s="28" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AA22" s="3">
         <v>100</v>
       </c>
       <c r="AB22" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AC22" s="2" t="s">
         <v>11</v>
@@ -6827,18 +6827,18 @@
       <c r="AE22" s="21" t="s">
         <v>5</v>
       </c>
-      <c r="AF22" s="63"/>
-      <c r="AG22" s="64"/>
-      <c r="AH22" s="64"/>
-      <c r="AI22" s="64"/>
-      <c r="AJ22" s="64"/>
-      <c r="AK22" s="64"/>
-      <c r="AL22" s="64"/>
-      <c r="AM22" s="64"/>
-      <c r="AN22" s="65"/>
+      <c r="AF22" s="88"/>
+      <c r="AG22" s="89"/>
+      <c r="AH22" s="89"/>
+      <c r="AI22" s="89"/>
+      <c r="AJ22" s="89"/>
+      <c r="AK22" s="89"/>
+      <c r="AL22" s="89"/>
+      <c r="AM22" s="89"/>
+      <c r="AN22" s="90"/>
     </row>
     <row r="23" spans="1:40" x14ac:dyDescent="0.25">
-      <c r="A23" s="52"/>
+      <c r="A23" s="77"/>
       <c r="B23" s="23" t="s">
         <v>9</v>
       </c>
@@ -6866,7 +6866,7 @@
       <c r="T23" s="21" t="s">
         <v>5</v>
       </c>
-      <c r="U23" s="52"/>
+      <c r="U23" s="77"/>
       <c r="V23" s="23" t="s">
         <v>9</v>
       </c>
@@ -6882,26 +6882,26 @@
       <c r="AE23" s="21" t="s">
         <v>5</v>
       </c>
-      <c r="AF23" s="63"/>
-      <c r="AG23" s="64"/>
-      <c r="AH23" s="64"/>
-      <c r="AI23" s="64"/>
-      <c r="AJ23" s="64"/>
-      <c r="AK23" s="64"/>
-      <c r="AL23" s="64"/>
-      <c r="AM23" s="64"/>
-      <c r="AN23" s="65"/>
+      <c r="AF23" s="88"/>
+      <c r="AG23" s="89"/>
+      <c r="AH23" s="89"/>
+      <c r="AI23" s="89"/>
+      <c r="AJ23" s="89"/>
+      <c r="AK23" s="89"/>
+      <c r="AL23" s="89"/>
+      <c r="AM23" s="89"/>
+      <c r="AN23" s="90"/>
     </row>
     <row r="24" spans="1:40" x14ac:dyDescent="0.25">
-      <c r="A24" s="52"/>
+      <c r="A24" s="77"/>
       <c r="B24" s="24" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C24" s="34">
         <v>323.3</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E24" s="6"/>
       <c r="F24" s="5"/>
@@ -6920,7 +6920,7 @@
         <v>356.8</v>
       </c>
       <c r="M24" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="N24" s="6"/>
       <c r="O24" s="5"/>
@@ -6935,15 +6935,15 @@
       <c r="T24" s="22" t="s">
         <v>5</v>
       </c>
-      <c r="U24" s="52"/>
+      <c r="U24" s="77"/>
       <c r="V24" s="24" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="W24" s="34">
         <v>346.7</v>
       </c>
       <c r="X24" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Y24" s="6"/>
       <c r="Z24" s="5"/>
@@ -6958,210 +6958,210 @@
       <c r="AE24" s="22" t="s">
         <v>5</v>
       </c>
-      <c r="AF24" s="66"/>
-      <c r="AG24" s="67"/>
-      <c r="AH24" s="67"/>
-      <c r="AI24" s="67"/>
-      <c r="AJ24" s="67"/>
-      <c r="AK24" s="67"/>
-      <c r="AL24" s="67"/>
-      <c r="AM24" s="67"/>
-      <c r="AN24" s="68"/>
+      <c r="AF24" s="91"/>
+      <c r="AG24" s="92"/>
+      <c r="AH24" s="92"/>
+      <c r="AI24" s="92"/>
+      <c r="AJ24" s="92"/>
+      <c r="AK24" s="92"/>
+      <c r="AL24" s="92"/>
+      <c r="AM24" s="92"/>
+      <c r="AN24" s="93"/>
     </row>
     <row r="25" spans="1:40" x14ac:dyDescent="0.25">
-      <c r="A25" s="52" t="s">
-        <v>62</v>
+      <c r="A25" s="77" t="s">
+        <v>61</v>
       </c>
       <c r="B25" s="27" t="s">
-        <v>31</v>
-      </c>
-      <c r="C25" s="53" t="s">
-        <v>40</v>
-      </c>
-      <c r="D25" s="54"/>
+        <v>30</v>
+      </c>
+      <c r="C25" s="75" t="s">
+        <v>39</v>
+      </c>
+      <c r="D25" s="76"/>
       <c r="E25" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="F25" s="41">
+        <v>0</v>
+      </c>
+      <c r="G25" s="39" t="s">
+        <v>33</v>
+      </c>
+      <c r="H25" s="41">
+        <v>0</v>
+      </c>
+      <c r="I25" s="39" t="s">
+        <v>34</v>
+      </c>
+      <c r="J25" s="41">
+        <v>0</v>
+      </c>
+      <c r="K25" s="39" t="s">
+        <v>35</v>
+      </c>
+      <c r="L25" s="75" t="s">
+        <v>39</v>
+      </c>
+      <c r="M25" s="76"/>
+      <c r="N25" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="O25" s="41">
+        <v>0</v>
+      </c>
+      <c r="P25" s="39" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q25" s="41">
+        <v>0</v>
+      </c>
+      <c r="R25" s="39" t="s">
+        <v>34</v>
+      </c>
+      <c r="S25" s="41">
+        <v>0</v>
+      </c>
+      <c r="T25" s="39" t="s">
+        <v>35</v>
+      </c>
+      <c r="U25" s="77" t="s">
+        <v>61</v>
+      </c>
+      <c r="V25" s="27" t="s">
+        <v>30</v>
+      </c>
+      <c r="W25" s="75" t="s">
+        <v>39</v>
+      </c>
+      <c r="X25" s="76"/>
+      <c r="Y25" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="Z25" s="41">
+        <v>0</v>
+      </c>
+      <c r="AA25" s="39" t="s">
+        <v>33</v>
+      </c>
+      <c r="AB25" s="41">
+        <v>0</v>
+      </c>
+      <c r="AC25" s="39" t="s">
+        <v>34</v>
+      </c>
+      <c r="AD25" s="41">
+        <v>0</v>
+      </c>
+      <c r="AE25" s="39" t="s">
+        <v>35</v>
+      </c>
+      <c r="AF25" s="75" t="s">
+        <v>39</v>
+      </c>
+      <c r="AG25" s="76"/>
+      <c r="AH25" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="AI25" s="41">
+        <v>0</v>
+      </c>
+      <c r="AJ25" s="39" t="s">
+        <v>33</v>
+      </c>
+      <c r="AK25" s="41">
+        <v>0</v>
+      </c>
+      <c r="AL25" s="39" t="s">
+        <v>34</v>
+      </c>
+      <c r="AM25" s="41">
+        <v>0</v>
+      </c>
+      <c r="AN25" s="42" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="26" spans="1:40" x14ac:dyDescent="0.25">
+      <c r="A26" s="77"/>
+      <c r="B26" s="24" t="s">
+        <v>29</v>
+      </c>
+      <c r="C26" s="78">
+        <v>0</v>
+      </c>
+      <c r="D26" s="74"/>
+      <c r="E26" s="40" t="s">
+        <v>43</v>
+      </c>
+      <c r="F26" s="29"/>
+      <c r="G26" s="74">
+        <v>0</v>
+      </c>
+      <c r="H26" s="74"/>
+      <c r="I26" s="74"/>
+      <c r="J26" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="F25" s="41">
-        <v>0</v>
-      </c>
-      <c r="G25" s="39" t="s">
-        <v>34</v>
-      </c>
-      <c r="H25" s="41">
-        <v>0</v>
-      </c>
-      <c r="I25" s="39" t="s">
-        <v>35</v>
-      </c>
-      <c r="J25" s="41">
-        <v>0</v>
-      </c>
-      <c r="K25" s="39" t="s">
-        <v>36</v>
-      </c>
-      <c r="L25" s="53" t="s">
-        <v>40</v>
-      </c>
-      <c r="M25" s="54"/>
-      <c r="N25" s="7" t="s">
+      <c r="K26" s="30"/>
+      <c r="L26" s="78">
+        <v>0</v>
+      </c>
+      <c r="M26" s="74"/>
+      <c r="N26" s="40" t="s">
+        <v>43</v>
+      </c>
+      <c r="O26" s="29"/>
+      <c r="P26" s="74">
+        <v>0</v>
+      </c>
+      <c r="Q26" s="74"/>
+      <c r="R26" s="74"/>
+      <c r="S26" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="O25" s="41">
-        <v>0</v>
-      </c>
-      <c r="P25" s="39" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q25" s="41">
-        <v>0</v>
-      </c>
-      <c r="R25" s="39" t="s">
-        <v>35</v>
-      </c>
-      <c r="S25" s="41">
-        <v>0</v>
-      </c>
-      <c r="T25" s="39" t="s">
-        <v>36</v>
-      </c>
-      <c r="U25" s="52" t="s">
-        <v>62</v>
-      </c>
-      <c r="V25" s="27" t="s">
-        <v>31</v>
-      </c>
-      <c r="W25" s="53" t="s">
-        <v>40</v>
-      </c>
-      <c r="X25" s="54"/>
-      <c r="Y25" s="7" t="s">
+      <c r="T26" s="30"/>
+      <c r="U26" s="77"/>
+      <c r="V26" s="24" t="s">
+        <v>29</v>
+      </c>
+      <c r="W26" s="78">
+        <v>0</v>
+      </c>
+      <c r="X26" s="74"/>
+      <c r="Y26" s="40" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z26" s="29"/>
+      <c r="AA26" s="74">
+        <v>0</v>
+      </c>
+      <c r="AB26" s="74"/>
+      <c r="AC26" s="74"/>
+      <c r="AD26" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="Z25" s="41">
-        <v>0</v>
-      </c>
-      <c r="AA25" s="39" t="s">
-        <v>34</v>
-      </c>
-      <c r="AB25" s="41">
-        <v>0</v>
-      </c>
-      <c r="AC25" s="39" t="s">
-        <v>35</v>
-      </c>
-      <c r="AD25" s="41">
-        <v>0</v>
-      </c>
-      <c r="AE25" s="39" t="s">
-        <v>36</v>
-      </c>
-      <c r="AF25" s="53" t="s">
-        <v>40</v>
-      </c>
-      <c r="AG25" s="54"/>
-      <c r="AH25" s="7" t="s">
+      <c r="AE26" s="30"/>
+      <c r="AF26" s="78">
+        <v>0</v>
+      </c>
+      <c r="AG26" s="74"/>
+      <c r="AH26" s="40" t="s">
+        <v>43</v>
+      </c>
+      <c r="AI26" s="29"/>
+      <c r="AJ26" s="74">
+        <v>0</v>
+      </c>
+      <c r="AK26" s="74"/>
+      <c r="AL26" s="74"/>
+      <c r="AM26" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="AI25" s="41">
-        <v>0</v>
-      </c>
-      <c r="AJ25" s="39" t="s">
-        <v>34</v>
-      </c>
-      <c r="AK25" s="41">
-        <v>0</v>
-      </c>
-      <c r="AL25" s="39" t="s">
-        <v>35</v>
-      </c>
-      <c r="AM25" s="41">
-        <v>0</v>
-      </c>
-      <c r="AN25" s="42" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="26" spans="1:40" x14ac:dyDescent="0.25">
-      <c r="A26" s="52"/>
-      <c r="B26" s="24" t="s">
-        <v>30</v>
-      </c>
-      <c r="C26" s="55">
-        <v>0</v>
-      </c>
-      <c r="D26" s="56"/>
-      <c r="E26" s="40" t="s">
-        <v>44</v>
-      </c>
-      <c r="F26" s="29"/>
-      <c r="G26" s="56">
-        <v>0</v>
-      </c>
-      <c r="H26" s="56"/>
-      <c r="I26" s="56"/>
-      <c r="J26" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="K26" s="30"/>
-      <c r="L26" s="55">
-        <v>0</v>
-      </c>
-      <c r="M26" s="56"/>
-      <c r="N26" s="40" t="s">
-        <v>44</v>
-      </c>
-      <c r="O26" s="29"/>
-      <c r="P26" s="56">
-        <v>0</v>
-      </c>
-      <c r="Q26" s="56"/>
-      <c r="R26" s="56"/>
-      <c r="S26" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="T26" s="30"/>
-      <c r="U26" s="52"/>
-      <c r="V26" s="24" t="s">
-        <v>30</v>
-      </c>
-      <c r="W26" s="55">
-        <v>0</v>
-      </c>
-      <c r="X26" s="56"/>
-      <c r="Y26" s="40" t="s">
-        <v>44</v>
-      </c>
-      <c r="Z26" s="29"/>
-      <c r="AA26" s="56">
-        <v>0</v>
-      </c>
-      <c r="AB26" s="56"/>
-      <c r="AC26" s="56"/>
-      <c r="AD26" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="AE26" s="30"/>
-      <c r="AF26" s="55">
-        <v>0</v>
-      </c>
-      <c r="AG26" s="56"/>
-      <c r="AH26" s="40" t="s">
-        <v>44</v>
-      </c>
-      <c r="AI26" s="29"/>
-      <c r="AJ26" s="56">
-        <v>0</v>
-      </c>
-      <c r="AK26" s="56"/>
-      <c r="AL26" s="56"/>
-      <c r="AM26" s="5" t="s">
-        <v>38</v>
-      </c>
       <c r="AN26" s="30"/>
     </row>
     <row r="27" spans="1:40" x14ac:dyDescent="0.25">
-      <c r="A27" s="52"/>
+      <c r="A27" s="77"/>
       <c r="B27" s="23" t="s">
         <v>10</v>
       </c>
@@ -7169,19 +7169,19 @@
         <v>67.3</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E27" s="3">
         <v>136</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G27" s="3">
         <v>4.6900000000000004</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I27" s="2" t="s">
         <v>11</v>
@@ -7196,19 +7196,19 @@
         <v>90.4</v>
       </c>
       <c r="M27" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="N27" s="3">
         <v>183.4</v>
       </c>
       <c r="O27" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="P27" s="3">
         <v>6.28</v>
       </c>
       <c r="Q27" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="R27" s="2" t="s">
         <v>11</v>
@@ -7219,27 +7219,27 @@
       <c r="T27" s="21" t="s">
         <v>5</v>
       </c>
-      <c r="U27" s="52"/>
+      <c r="U27" s="77"/>
       <c r="V27" s="23" t="s">
         <v>10</v>
       </c>
       <c r="W27" s="48" t="s">
+        <v>63</v>
+      </c>
+      <c r="X27" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="Y27" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="X27" s="2" t="s">
+      <c r="Z27" s="2" t="s">
         <v>21</v>
-      </c>
-      <c r="Y27" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="Z27" s="2" t="s">
-        <v>22</v>
       </c>
       <c r="AA27" s="3">
         <v>14.71</v>
       </c>
       <c r="AB27" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AC27" s="2" t="s">
         <v>11</v>
@@ -7254,19 +7254,19 @@
         <v>34.799999999999997</v>
       </c>
       <c r="AG27" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AH27" s="3">
         <v>70.2</v>
       </c>
       <c r="AI27" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AJ27" s="3">
         <v>2.31</v>
       </c>
       <c r="AK27" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AL27" s="2" t="s">
         <v>11</v>
@@ -7279,7 +7279,7 @@
       </c>
     </row>
     <row r="28" spans="1:40" x14ac:dyDescent="0.25">
-      <c r="A28" s="52"/>
+      <c r="A28" s="77"/>
       <c r="B28" s="23" t="s">
         <v>8</v>
       </c>
@@ -7287,7 +7287,7 @@
         <v>128.9</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I28" s="2" t="s">
         <v>11</v>
@@ -7302,7 +7302,7 @@
         <v>140.5</v>
       </c>
       <c r="M28" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="R28" s="2" t="s">
         <v>11</v>
@@ -7313,7 +7313,7 @@
       <c r="T28" s="21" t="s">
         <v>5</v>
       </c>
-      <c r="U28" s="52"/>
+      <c r="U28" s="77"/>
       <c r="V28" s="23" t="s">
         <v>8</v>
       </c>
@@ -7321,7 +7321,7 @@
         <v>124.7</v>
       </c>
       <c r="X28" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AC28" s="2" t="s">
         <v>11</v>
@@ -7336,7 +7336,7 @@
         <v>129.80000000000001</v>
       </c>
       <c r="AG28" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AL28" s="2" t="s">
         <v>11</v>
@@ -7349,24 +7349,24 @@
       </c>
     </row>
     <row r="29" spans="1:40" x14ac:dyDescent="0.25">
-      <c r="A29" s="52"/>
+      <c r="A29" s="77"/>
       <c r="B29" s="23" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C29" s="33">
         <v>7.76</v>
       </c>
       <c r="D29" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E29" s="28" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G29" s="3">
         <v>129</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I29" s="2" t="s">
         <v>11</v>
@@ -7381,16 +7381,16 @@
         <v>7.13</v>
       </c>
       <c r="M29" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="N29" s="28" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="P29" s="3">
         <v>141</v>
       </c>
       <c r="Q29" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="R29" s="2" t="s">
         <v>11</v>
@@ -7401,24 +7401,24 @@
       <c r="T29" s="21" t="s">
         <v>5</v>
       </c>
-      <c r="U29" s="52"/>
+      <c r="U29" s="77"/>
       <c r="V29" s="23" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="W29" s="33">
         <v>8.01</v>
       </c>
       <c r="X29" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y29" s="28" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AA29" s="3">
         <v>125</v>
       </c>
       <c r="AB29" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AC29" s="2" t="s">
         <v>11</v>
@@ -7433,16 +7433,16 @@
         <v>7.71</v>
       </c>
       <c r="AG29" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AH29" s="28" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AJ29" s="3">
         <v>130</v>
       </c>
       <c r="AK29" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AL29" s="2" t="s">
         <v>11</v>
@@ -7455,7 +7455,7 @@
       </c>
     </row>
     <row r="30" spans="1:40" x14ac:dyDescent="0.25">
-      <c r="A30" s="52"/>
+      <c r="A30" s="77"/>
       <c r="B30" s="23" t="s">
         <v>9</v>
       </c>
@@ -7483,7 +7483,7 @@
       <c r="T30" s="21" t="s">
         <v>5</v>
       </c>
-      <c r="U30" s="52"/>
+      <c r="U30" s="77"/>
       <c r="V30" s="23" t="s">
         <v>9</v>
       </c>
@@ -7513,15 +7513,15 @@
       </c>
     </row>
     <row r="31" spans="1:40" x14ac:dyDescent="0.25">
-      <c r="A31" s="52"/>
+      <c r="A31" s="77"/>
       <c r="B31" s="24" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C31" s="34">
         <v>336.4</v>
       </c>
       <c r="D31" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E31" s="6"/>
       <c r="F31" s="5"/>
@@ -7540,7 +7540,7 @@
         <v>326.60000000000002</v>
       </c>
       <c r="M31" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="N31" s="6"/>
       <c r="O31" s="5"/>
@@ -7555,15 +7555,15 @@
       <c r="T31" s="22" t="s">
         <v>5</v>
       </c>
-      <c r="U31" s="52"/>
+      <c r="U31" s="77"/>
       <c r="V31" s="24" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="W31" s="34">
         <v>325.60000000000002</v>
       </c>
       <c r="X31" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Y31" s="6"/>
       <c r="Z31" s="5"/>
@@ -7582,7 +7582,7 @@
         <v>257.60000000000002</v>
       </c>
       <c r="AG31" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AH31" s="6"/>
       <c r="AI31" s="5"/>
@@ -7600,7 +7600,7 @@
     </row>
     <row r="33" spans="32:40" x14ac:dyDescent="0.25">
       <c r="AF33" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="34" spans="32:40" x14ac:dyDescent="0.25">
@@ -7616,44 +7616,6 @@
     </row>
   </sheetData>
   <mergeCells count="54">
-    <mergeCell ref="AJ26:AL26"/>
-    <mergeCell ref="W19:X19"/>
-    <mergeCell ref="AA19:AC19"/>
-    <mergeCell ref="W18:X18"/>
-    <mergeCell ref="W25:X25"/>
-    <mergeCell ref="W26:X26"/>
-    <mergeCell ref="AA26:AC26"/>
-    <mergeCell ref="AF25:AG25"/>
-    <mergeCell ref="AF26:AG26"/>
-    <mergeCell ref="AF18:AN24"/>
-    <mergeCell ref="AF4:AN10"/>
-    <mergeCell ref="W12:X12"/>
-    <mergeCell ref="AA12:AC12"/>
-    <mergeCell ref="AF11:AN17"/>
-    <mergeCell ref="L18:M18"/>
-    <mergeCell ref="L11:M11"/>
-    <mergeCell ref="AA5:AC5"/>
-    <mergeCell ref="L19:M19"/>
-    <mergeCell ref="P19:R19"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="G12:I12"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="G19:I19"/>
-    <mergeCell ref="L12:M12"/>
-    <mergeCell ref="P12:R12"/>
-    <mergeCell ref="C26:D26"/>
-    <mergeCell ref="G26:I26"/>
-    <mergeCell ref="L25:M25"/>
-    <mergeCell ref="L26:M26"/>
-    <mergeCell ref="P26:R26"/>
-    <mergeCell ref="C5:D5"/>
-    <mergeCell ref="G5:I5"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="W11:X11"/>
-    <mergeCell ref="P5:R5"/>
-    <mergeCell ref="W5:X5"/>
     <mergeCell ref="A18:A24"/>
     <mergeCell ref="U18:U24"/>
     <mergeCell ref="A25:A31"/>
@@ -7670,6 +7632,44 @@
     <mergeCell ref="A11:A17"/>
     <mergeCell ref="U11:U17"/>
     <mergeCell ref="L5:M5"/>
+    <mergeCell ref="C5:D5"/>
+    <mergeCell ref="G5:I5"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="W11:X11"/>
+    <mergeCell ref="P5:R5"/>
+    <mergeCell ref="W5:X5"/>
+    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="G26:I26"/>
+    <mergeCell ref="L25:M25"/>
+    <mergeCell ref="L26:M26"/>
+    <mergeCell ref="P26:R26"/>
+    <mergeCell ref="L19:M19"/>
+    <mergeCell ref="P19:R19"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="G12:I12"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="G19:I19"/>
+    <mergeCell ref="L12:M12"/>
+    <mergeCell ref="P12:R12"/>
+    <mergeCell ref="AF4:AN10"/>
+    <mergeCell ref="W12:X12"/>
+    <mergeCell ref="AA12:AC12"/>
+    <mergeCell ref="AF11:AN17"/>
+    <mergeCell ref="L18:M18"/>
+    <mergeCell ref="L11:M11"/>
+    <mergeCell ref="AA5:AC5"/>
+    <mergeCell ref="AJ26:AL26"/>
+    <mergeCell ref="W19:X19"/>
+    <mergeCell ref="AA19:AC19"/>
+    <mergeCell ref="W18:X18"/>
+    <mergeCell ref="W25:X25"/>
+    <mergeCell ref="W26:X26"/>
+    <mergeCell ref="AA26:AC26"/>
+    <mergeCell ref="AF25:AG25"/>
+    <mergeCell ref="AF26:AG26"/>
+    <mergeCell ref="AF18:AN24"/>
   </mergeCells>
   <pageMargins left="0.19685039370078741" right="0.11811023622047245" top="0.78740157480314965" bottom="0.78740157480314965" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>
@@ -7688,33 +7688,33 @@
   <sheetData>
     <row r="1" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="35" t="s">
-        <v>19</v>
+        <v>104</v>
       </c>
       <c r="B1" s="9"/>
     </row>
     <row r="2" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A3" s="83" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="86" t="s">
+      <c r="A3" s="61" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="64" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="87"/>
-      <c r="D3" s="85" t="s">
+      <c r="C3" s="65"/>
+      <c r="D3" s="63" t="s">
         <v>2</v>
       </c>
-      <c r="E3" s="85"/>
-      <c r="F3" s="85"/>
-      <c r="G3" s="80" t="s">
+      <c r="E3" s="63"/>
+      <c r="F3" s="63"/>
+      <c r="G3" s="58" t="s">
         <v>3</v>
       </c>
-      <c r="H3" s="81"/>
-      <c r="I3" s="81"/>
-      <c r="J3" s="82"/>
+      <c r="H3" s="59"/>
+      <c r="I3" s="59"/>
+      <c r="J3" s="60"/>
     </row>
     <row r="4" spans="1:10" s="15" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="84"/>
+      <c r="A4" s="62"/>
       <c r="B4" s="10" t="s">
         <v>15</v>
       </c>
@@ -7744,293 +7744,286 @@
       </c>
     </row>
     <row r="5" spans="1:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="A5" s="88" t="s">
-        <v>43</v>
+      <c r="A5" s="66" t="s">
+        <v>42</v>
       </c>
       <c r="B5" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="C5" s="19" t="s">
         <v>72</v>
       </c>
-      <c r="C5" s="19" t="s">
+      <c r="D5" s="16" t="s">
         <v>73</v>
       </c>
-      <c r="D5" s="16" t="s">
+      <c r="E5" s="20" t="s">
         <v>74</v>
       </c>
-      <c r="E5" s="20" t="s">
+      <c r="F5" s="19" t="s">
         <v>75</v>
       </c>
-      <c r="F5" s="19" t="s">
+      <c r="G5" s="16" t="s">
         <v>76</v>
       </c>
-      <c r="G5" s="16" t="s">
+      <c r="H5" s="18" t="s">
         <v>77</v>
       </c>
-      <c r="H5" s="18" t="s">
+      <c r="I5" s="17" t="s">
         <v>78</v>
       </c>
-      <c r="I5" s="17" t="s">
+      <c r="J5" s="19" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="67"/>
+      <c r="B6" s="69" t="s">
+        <v>69</v>
+      </c>
+      <c r="C6" s="70"/>
+      <c r="D6" s="69" t="s">
+        <v>70</v>
+      </c>
+      <c r="E6" s="70"/>
+      <c r="F6" s="71"/>
+      <c r="G6" s="69" t="s">
+        <v>70</v>
+      </c>
+      <c r="H6" s="70"/>
+      <c r="I6" s="70"/>
+      <c r="J6" s="71"/>
+    </row>
+    <row r="7" spans="1:10" ht="28.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="68"/>
+      <c r="B7" s="55" t="s">
+        <v>48</v>
+      </c>
+      <c r="C7" s="56"/>
+      <c r="D7" s="55" t="s">
+        <v>49</v>
+      </c>
+      <c r="E7" s="57"/>
+      <c r="F7" s="56"/>
+      <c r="G7" s="55" t="s">
+        <v>50</v>
+      </c>
+      <c r="H7" s="57"/>
+      <c r="I7" s="57"/>
+      <c r="J7" s="56"/>
+    </row>
+    <row r="8" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="A8" s="49" t="s">
+        <v>46</v>
+      </c>
+      <c r="B8" s="43" t="s">
         <v>79</v>
       </c>
-      <c r="J5" s="19" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="89"/>
-      <c r="B6" s="91" t="s">
-        <v>70</v>
-      </c>
-      <c r="C6" s="92"/>
-      <c r="D6" s="91" t="s">
-        <v>71</v>
-      </c>
-      <c r="E6" s="92"/>
-      <c r="F6" s="93"/>
-      <c r="G6" s="91" t="s">
-        <v>71</v>
-      </c>
-      <c r="H6" s="92"/>
-      <c r="I6" s="92"/>
-      <c r="J6" s="93"/>
-    </row>
-    <row r="7" spans="1:10" ht="28.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="90"/>
-      <c r="B7" s="77" t="s">
-        <v>49</v>
-      </c>
-      <c r="C7" s="79"/>
-      <c r="D7" s="77" t="s">
-        <v>50</v>
-      </c>
-      <c r="E7" s="78"/>
-      <c r="F7" s="79"/>
-      <c r="G7" s="77" t="s">
+      <c r="C8" s="44" t="s">
+        <v>80</v>
+      </c>
+      <c r="D8" s="43" t="s">
+        <v>81</v>
+      </c>
+      <c r="E8" s="45" t="s">
+        <v>82</v>
+      </c>
+      <c r="F8" s="46" t="s">
+        <v>83</v>
+      </c>
+      <c r="G8" s="45" t="s">
+        <v>86</v>
+      </c>
+      <c r="H8" s="44" t="s">
+        <v>85</v>
+      </c>
+      <c r="I8" s="47" t="s">
+        <v>84</v>
+      </c>
+      <c r="J8" s="46" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A9" s="50"/>
+      <c r="B9" s="52" t="s">
+        <v>47</v>
+      </c>
+      <c r="C9" s="53"/>
+      <c r="D9" s="52" t="s">
+        <v>47</v>
+      </c>
+      <c r="E9" s="54"/>
+      <c r="F9" s="53"/>
+      <c r="G9" s="52" t="s">
+        <v>47</v>
+      </c>
+      <c r="H9" s="54"/>
+      <c r="I9" s="54"/>
+      <c r="J9" s="53"/>
+    </row>
+    <row r="10" spans="1:10" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="51"/>
+      <c r="B10" s="55" t="s">
         <v>51</v>
       </c>
-      <c r="H7" s="78"/>
-      <c r="I7" s="78"/>
-      <c r="J7" s="79"/>
-    </row>
-    <row r="8" spans="1:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="A8" s="69" t="s">
-        <v>47</v>
-      </c>
-      <c r="B8" s="43" t="s">
-        <v>80</v>
-      </c>
-      <c r="C8" s="44" t="s">
-        <v>81</v>
-      </c>
-      <c r="D8" s="43" t="s">
-        <v>82</v>
-      </c>
-      <c r="E8" s="45" t="s">
-        <v>83</v>
-      </c>
-      <c r="F8" s="46" t="s">
-        <v>84</v>
-      </c>
-      <c r="G8" s="45" t="s">
+      <c r="C10" s="56"/>
+      <c r="D10" s="55" t="s">
+        <v>52</v>
+      </c>
+      <c r="E10" s="57"/>
+      <c r="F10" s="56"/>
+      <c r="G10" s="55" t="s">
+        <v>53</v>
+      </c>
+      <c r="H10" s="57"/>
+      <c r="I10" s="57"/>
+      <c r="J10" s="56"/>
+    </row>
+    <row r="11" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="A11" s="49" t="s">
+        <v>56</v>
+      </c>
+      <c r="B11" s="43" t="s">
+        <v>94</v>
+      </c>
+      <c r="C11" s="44" t="s">
+        <v>93</v>
+      </c>
+      <c r="D11" s="43" t="s">
+        <v>92</v>
+      </c>
+      <c r="E11" s="45" t="s">
+        <v>91</v>
+      </c>
+      <c r="F11" s="46" t="s">
+        <v>90</v>
+      </c>
+      <c r="G11" s="45" t="s">
+        <v>89</v>
+      </c>
+      <c r="H11" s="44" t="s">
+        <v>88</v>
+      </c>
+      <c r="I11" s="47" t="s">
         <v>87</v>
       </c>
-      <c r="H8" s="44" t="s">
-        <v>86</v>
-      </c>
-      <c r="I8" s="47" t="s">
-        <v>85</v>
-      </c>
-      <c r="J8" s="46" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A9" s="70"/>
-      <c r="B9" s="72" t="s">
-        <v>48</v>
-      </c>
-      <c r="C9" s="73"/>
-      <c r="D9" s="72" t="s">
-        <v>48</v>
-      </c>
-      <c r="E9" s="74"/>
-      <c r="F9" s="73"/>
-      <c r="G9" s="72" t="s">
-        <v>48</v>
-      </c>
-      <c r="H9" s="74"/>
-      <c r="I9" s="74"/>
-      <c r="J9" s="73"/>
-    </row>
-    <row r="10" spans="1:10" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="71"/>
-      <c r="B10" s="77" t="s">
-        <v>52</v>
-      </c>
-      <c r="C10" s="79"/>
-      <c r="D10" s="77" t="s">
-        <v>53</v>
-      </c>
-      <c r="E10" s="78"/>
-      <c r="F10" s="79"/>
-      <c r="G10" s="77" t="s">
-        <v>54</v>
-      </c>
-      <c r="H10" s="78"/>
-      <c r="I10" s="78"/>
-      <c r="J10" s="79"/>
-    </row>
-    <row r="11" spans="1:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="A11" s="69" t="s">
+      <c r="J11" s="46" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A12" s="50"/>
+      <c r="B12" s="52" t="s">
+        <v>60</v>
+      </c>
+      <c r="C12" s="53"/>
+      <c r="D12" s="52" t="s">
+        <v>60</v>
+      </c>
+      <c r="E12" s="54"/>
+      <c r="F12" s="53"/>
+      <c r="G12" s="52" t="s">
+        <v>60</v>
+      </c>
+      <c r="H12" s="54"/>
+      <c r="I12" s="54"/>
+      <c r="J12" s="53"/>
+    </row>
+    <row r="13" spans="1:10" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="51"/>
+      <c r="B13" s="55" t="s">
         <v>57</v>
       </c>
-      <c r="B11" s="43" t="s">
+      <c r="C13" s="56"/>
+      <c r="D13" s="55" t="s">
+        <v>58</v>
+      </c>
+      <c r="E13" s="57"/>
+      <c r="F13" s="56"/>
+      <c r="G13" s="55" t="s">
+        <v>59</v>
+      </c>
+      <c r="H13" s="57"/>
+      <c r="I13" s="57"/>
+      <c r="J13" s="56"/>
+    </row>
+    <row r="14" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="A14" s="49" t="s">
+        <v>56</v>
+      </c>
+      <c r="B14" s="43" t="s">
+        <v>103</v>
+      </c>
+      <c r="C14" s="44" t="s">
+        <v>102</v>
+      </c>
+      <c r="D14" s="43" t="s">
+        <v>101</v>
+      </c>
+      <c r="E14" s="45" t="s">
+        <v>100</v>
+      </c>
+      <c r="F14" s="46" t="s">
+        <v>99</v>
+      </c>
+      <c r="G14" s="45" t="s">
         <v>95</v>
       </c>
-      <c r="C11" s="44" t="s">
-        <v>94</v>
-      </c>
-      <c r="D11" s="43" t="s">
-        <v>93</v>
-      </c>
-      <c r="E11" s="45" t="s">
-        <v>92</v>
-      </c>
-      <c r="F11" s="46" t="s">
-        <v>91</v>
-      </c>
-      <c r="G11" s="45" t="s">
-        <v>90</v>
-      </c>
-      <c r="H11" s="44" t="s">
-        <v>89</v>
-      </c>
-      <c r="I11" s="47" t="s">
-        <v>88</v>
-      </c>
-      <c r="J11" s="46" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A12" s="70"/>
-      <c r="B12" s="72" t="s">
-        <v>61</v>
-      </c>
-      <c r="C12" s="73"/>
-      <c r="D12" s="72" t="s">
-        <v>61</v>
-      </c>
-      <c r="E12" s="74"/>
-      <c r="F12" s="73"/>
-      <c r="G12" s="72" t="s">
-        <v>61</v>
-      </c>
-      <c r="H12" s="74"/>
-      <c r="I12" s="74"/>
-      <c r="J12" s="73"/>
-    </row>
-    <row r="13" spans="1:10" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="71"/>
-      <c r="B13" s="77" t="s">
-        <v>58</v>
-      </c>
-      <c r="C13" s="79"/>
-      <c r="D13" s="77" t="s">
-        <v>59</v>
-      </c>
-      <c r="E13" s="78"/>
-      <c r="F13" s="79"/>
-      <c r="G13" s="77" t="s">
-        <v>60</v>
-      </c>
-      <c r="H13" s="78"/>
-      <c r="I13" s="78"/>
-      <c r="J13" s="79"/>
-    </row>
-    <row r="14" spans="1:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="A14" s="69" t="s">
-        <v>57</v>
-      </c>
-      <c r="B14" s="43" t="s">
-        <v>104</v>
-      </c>
-      <c r="C14" s="44" t="s">
-        <v>103</v>
-      </c>
-      <c r="D14" s="43" t="s">
-        <v>102</v>
-      </c>
-      <c r="E14" s="45" t="s">
-        <v>101</v>
-      </c>
-      <c r="F14" s="46" t="s">
-        <v>100</v>
-      </c>
-      <c r="G14" s="45" t="s">
+      <c r="H14" s="44" t="s">
         <v>96</v>
       </c>
-      <c r="H14" s="44" t="s">
+      <c r="I14" s="47" t="s">
+        <v>98</v>
+      </c>
+      <c r="J14" s="46" t="s">
         <v>97</v>
       </c>
-      <c r="I14" s="47" t="s">
-        <v>99</v>
-      </c>
-      <c r="J14" s="46" t="s">
-        <v>98</v>
-      </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A15" s="70"/>
-      <c r="B15" s="72" t="s">
-        <v>69</v>
-      </c>
-      <c r="C15" s="73"/>
-      <c r="D15" s="72" t="s">
-        <v>69</v>
-      </c>
-      <c r="E15" s="74"/>
-      <c r="F15" s="73"/>
-      <c r="G15" s="72" t="s">
-        <v>69</v>
-      </c>
-      <c r="H15" s="74"/>
-      <c r="I15" s="74"/>
-      <c r="J15" s="73"/>
+      <c r="A15" s="50"/>
+      <c r="B15" s="52" t="s">
+        <v>68</v>
+      </c>
+      <c r="C15" s="53"/>
+      <c r="D15" s="52" t="s">
+        <v>68</v>
+      </c>
+      <c r="E15" s="54"/>
+      <c r="F15" s="53"/>
+      <c r="G15" s="52" t="s">
+        <v>68</v>
+      </c>
+      <c r="H15" s="54"/>
+      <c r="I15" s="54"/>
+      <c r="J15" s="53"/>
     </row>
     <row r="16" spans="1:10" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="71"/>
-      <c r="B16" s="75" t="s">
+      <c r="A16" s="51"/>
+      <c r="B16" s="72" t="s">
+        <v>66</v>
+      </c>
+      <c r="C16" s="73"/>
+      <c r="D16" s="55" t="s">
+        <v>66</v>
+      </c>
+      <c r="E16" s="57"/>
+      <c r="F16" s="56"/>
+      <c r="G16" s="55" t="s">
         <v>67</v>
       </c>
-      <c r="C16" s="76"/>
-      <c r="D16" s="77" t="s">
-        <v>67</v>
-      </c>
-      <c r="E16" s="78"/>
-      <c r="F16" s="79"/>
-      <c r="G16" s="77" t="s">
-        <v>68</v>
-      </c>
-      <c r="H16" s="78"/>
-      <c r="I16" s="78"/>
-      <c r="J16" s="79"/>
+      <c r="H16" s="57"/>
+      <c r="I16" s="57"/>
+      <c r="J16" s="56"/>
     </row>
   </sheetData>
   <mergeCells count="32">
-    <mergeCell ref="A11:A13"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="D12:F12"/>
-    <mergeCell ref="G12:J12"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="D13:F13"/>
-    <mergeCell ref="G13:J13"/>
-    <mergeCell ref="A8:A10"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="D9:F9"/>
-    <mergeCell ref="G9:J9"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="D10:F10"/>
-    <mergeCell ref="G10:J10"/>
+    <mergeCell ref="A14:A16"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="D15:F15"/>
+    <mergeCell ref="G15:J15"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="D16:F16"/>
+    <mergeCell ref="G16:J16"/>
     <mergeCell ref="G3:J3"/>
     <mergeCell ref="A3:A4"/>
     <mergeCell ref="D3:F3"/>
@@ -8042,13 +8035,20 @@
     <mergeCell ref="D6:F6"/>
     <mergeCell ref="G6:J6"/>
     <mergeCell ref="G7:J7"/>
-    <mergeCell ref="A14:A16"/>
-    <mergeCell ref="B15:C15"/>
-    <mergeCell ref="D15:F15"/>
-    <mergeCell ref="G15:J15"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="D16:F16"/>
-    <mergeCell ref="G16:J16"/>
+    <mergeCell ref="A8:A10"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="D9:F9"/>
+    <mergeCell ref="G9:J9"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="D10:F10"/>
+    <mergeCell ref="G10:J10"/>
+    <mergeCell ref="A11:A13"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="D12:F12"/>
+    <mergeCell ref="G12:J12"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="D13:F13"/>
+    <mergeCell ref="G13:J13"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>
